--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L525"/>
+  <dimension ref="A1:L528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17973,6 +17973,100 @@
       <c r="K525" t="inlineStr"/>
       <c r="L525" t="inlineStr"/>
     </row>
+    <row r="526">
+      <c r="A526" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B526" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C526" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D526" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E526" t="n">
+        <v>465.80531254</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G526" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H526" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I526" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J526" t="inlineStr"/>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B527" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C527" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D527" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E527" t="n">
+        <v>465.80531254</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G527" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H527" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I527" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J527" t="inlineStr"/>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B528" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C528" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D528" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G528" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H528" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I528" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J528" t="inlineStr"/>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L528"/>
+  <dimension ref="A1:M530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,15 +477,20 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MANTRAUSDT</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>ZECUSDT</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>BBUSDT</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>JASMYUSDT</t>
         </is>
@@ -518,10 +523,11 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M2" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -552,10 +558,11 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M3" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -586,10 +593,11 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M4" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -620,10 +628,11 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M5" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -654,10 +663,11 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M6" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -688,10 +698,11 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M7" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -722,10 +733,11 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M8" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -756,10 +768,11 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M9" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -790,10 +803,11 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M10" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -824,10 +838,11 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M11" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -858,10 +873,11 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M12" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -892,10 +908,11 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M13" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -926,10 +943,11 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M14" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -960,10 +978,11 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M15" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -994,10 +1013,11 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M16" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1028,10 +1048,11 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M17" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1062,10 +1083,11 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M18" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1096,10 +1118,11 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M19" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1130,10 +1153,11 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M20" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1164,10 +1188,11 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M21" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1198,10 +1223,11 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M22" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1232,10 +1258,11 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M23" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1266,10 +1293,11 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M24" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1300,10 +1328,11 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M25" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1334,10 +1363,11 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M26" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1368,10 +1398,11 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M27" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1402,10 +1433,11 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M28" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1436,10 +1468,11 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M29" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1470,10 +1503,11 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M30" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1504,10 +1538,11 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M31" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1538,10 +1573,11 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M32" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1572,10 +1608,11 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M33" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1606,10 +1643,11 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M34" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1640,10 +1678,11 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M35" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1674,10 +1713,11 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M36" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1708,10 +1748,11 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M37" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1742,10 +1783,11 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M38" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1776,10 +1818,11 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M39" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1810,10 +1853,11 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M40" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1844,10 +1888,11 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M41" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1878,10 +1923,11 @@
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M42" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1912,10 +1958,11 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M43" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1946,10 +1993,11 @@
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M44" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -1980,10 +2028,11 @@
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M45" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2014,10 +2063,11 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M46" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2048,10 +2098,11 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M47" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2082,10 +2133,11 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M48" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2116,10 +2168,11 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M49" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2150,10 +2203,11 @@
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M50" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2184,10 +2238,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M51" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2218,10 +2273,11 @@
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M52" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2252,10 +2308,11 @@
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M53" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2286,10 +2343,11 @@
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M54" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2320,10 +2378,11 @@
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M55" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2354,10 +2413,11 @@
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M56" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2388,10 +2448,11 @@
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M57" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2422,10 +2483,11 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M58" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2456,10 +2518,11 @@
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M59" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2490,10 +2553,11 @@
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M60" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2524,10 +2588,11 @@
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M61" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2558,10 +2623,11 @@
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M62" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2592,10 +2658,11 @@
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M63" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2626,10 +2693,11 @@
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M64" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2660,10 +2728,11 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M65" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2694,10 +2763,11 @@
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M66" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2728,10 +2798,11 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M67" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2762,10 +2833,11 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M68" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2796,10 +2868,11 @@
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M69" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2830,10 +2903,11 @@
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M70" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2864,10 +2938,11 @@
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M71" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2898,10 +2973,11 @@
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M72" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2932,10 +3008,11 @@
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M73" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -2966,10 +3043,11 @@
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M74" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3000,10 +3078,11 @@
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M75" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3034,10 +3113,11 @@
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M76" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3068,10 +3148,11 @@
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K77" t="inlineStr"/>
       <c r="L77" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M77" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3102,10 +3183,11 @@
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M78" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3136,10 +3218,11 @@
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M79" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3170,10 +3253,11 @@
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M80" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3204,10 +3288,11 @@
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M81" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3238,10 +3323,11 @@
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M82" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3272,10 +3358,11 @@
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M83" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3306,10 +3393,11 @@
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M84" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3340,10 +3428,11 @@
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M85" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3374,10 +3463,11 @@
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M86" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3408,10 +3498,11 @@
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
-      <c r="K87" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K87" t="inlineStr"/>
       <c r="L87" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M87" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3442,10 +3533,11 @@
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M88" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3476,10 +3568,11 @@
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M89" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3510,10 +3603,11 @@
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M90" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3544,10 +3638,11 @@
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M91" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3578,10 +3673,11 @@
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M92" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3612,10 +3708,11 @@
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M93" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3646,10 +3743,11 @@
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M94" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3680,10 +3778,11 @@
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M95" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3714,10 +3813,11 @@
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M96" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3748,10 +3848,11 @@
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M97" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3782,10 +3883,11 @@
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
-      <c r="K98" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M98" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3816,10 +3918,11 @@
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M99" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3850,10 +3953,11 @@
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M100" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3884,10 +3988,11 @@
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
-      <c r="K101" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M101" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3918,10 +4023,11 @@
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M102" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3952,10 +4058,11 @@
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
-      <c r="K103" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M103" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -3986,10 +4093,11 @@
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M104" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4020,10 +4128,11 @@
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M105" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4054,10 +4163,11 @@
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M106" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4088,10 +4198,11 @@
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M107" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4122,10 +4233,11 @@
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M108" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4156,10 +4268,11 @@
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M109" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4190,10 +4303,11 @@
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M110" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4224,10 +4338,11 @@
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M111" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4258,10 +4373,11 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="L112" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M112" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4292,10 +4408,11 @@
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M113" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4326,10 +4443,11 @@
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M114" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4360,10 +4478,11 @@
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M115" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4394,10 +4513,11 @@
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M116" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4428,10 +4548,11 @@
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M117" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4462,10 +4583,11 @@
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M118" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4496,10 +4618,11 @@
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M119" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4530,10 +4653,11 @@
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M120" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4564,10 +4688,11 @@
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K121" t="inlineStr"/>
       <c r="L121" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M121" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4598,10 +4723,11 @@
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M122" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4632,10 +4758,11 @@
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
-      <c r="K123" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K123" t="inlineStr"/>
       <c r="L123" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M123" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4666,10 +4793,11 @@
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M124" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4700,10 +4828,11 @@
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M125" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4734,10 +4863,11 @@
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
-      <c r="K126" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M126" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4768,10 +4898,11 @@
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M127" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4802,10 +4933,11 @@
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M128" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4836,10 +4968,11 @@
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M129" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4870,10 +5003,11 @@
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
-      <c r="K130" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M130" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4904,10 +5038,11 @@
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
-      <c r="K131" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M131" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4938,10 +5073,11 @@
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M132" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -4972,10 +5108,11 @@
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M133" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5006,10 +5143,11 @@
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M134" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5040,10 +5178,11 @@
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M135" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5074,10 +5213,11 @@
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
-      <c r="K136" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M136" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5108,10 +5248,11 @@
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M137" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5142,10 +5283,11 @@
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
-      <c r="K138" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M138" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5176,10 +5318,11 @@
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M139" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5210,10 +5353,11 @@
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
-      <c r="K140" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M140" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5244,10 +5388,11 @@
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M141" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5278,10 +5423,11 @@
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K142" t="inlineStr"/>
       <c r="L142" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M142" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5312,10 +5458,11 @@
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="L143" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M143" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5346,10 +5493,11 @@
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="L144" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M144" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5380,10 +5528,11 @@
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M145" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5414,10 +5563,11 @@
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
-      <c r="K146" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M146" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5448,10 +5598,11 @@
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M147" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5482,10 +5633,11 @@
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
-      <c r="K148" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K148" t="inlineStr"/>
       <c r="L148" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M148" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5516,10 +5668,11 @@
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
-      <c r="K149" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M149" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5550,10 +5703,11 @@
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
-      <c r="K150" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M150" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5584,10 +5738,11 @@
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M151" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5618,10 +5773,11 @@
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
-      <c r="K152" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M152" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5652,10 +5808,11 @@
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
-      <c r="K153" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M153" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5686,10 +5843,11 @@
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M154" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5720,10 +5878,11 @@
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
-      <c r="K155" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K155" t="inlineStr"/>
       <c r="L155" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M155" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5754,10 +5913,11 @@
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
-      <c r="K156" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M156" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5788,10 +5948,11 @@
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
-      <c r="K157" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M157" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5822,10 +5983,11 @@
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
-      <c r="K158" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M158" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5856,10 +6018,11 @@
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
-      <c r="K159" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K159" t="inlineStr"/>
       <c r="L159" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M159" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5890,10 +6053,11 @@
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
-      <c r="K160" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M160" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5924,10 +6088,11 @@
       </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
-      <c r="K161" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M161" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5958,10 +6123,11 @@
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
-      <c r="K162" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K162" t="inlineStr"/>
       <c r="L162" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M162" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -5992,10 +6158,11 @@
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
-      <c r="K163" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M163" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6026,10 +6193,11 @@
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
-      <c r="K164" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K164" t="inlineStr"/>
       <c r="L164" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M164" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6060,10 +6228,11 @@
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
-      <c r="K165" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M165" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6094,10 +6263,11 @@
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
-      <c r="K166" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M166" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6128,10 +6298,11 @@
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr"/>
-      <c r="K167" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M167" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6162,10 +6333,11 @@
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr"/>
-      <c r="K168" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M168" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6196,10 +6368,11 @@
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr"/>
-      <c r="K169" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M169" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6230,10 +6403,11 @@
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M170" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6264,10 +6438,11 @@
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M171" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6298,10 +6473,11 @@
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr"/>
-      <c r="K172" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M172" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6332,10 +6508,11 @@
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr"/>
-      <c r="K173" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M173" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6366,10 +6543,11 @@
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M174" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6400,10 +6578,11 @@
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
-      <c r="K175" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M175" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6434,10 +6613,11 @@
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M176" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6468,10 +6648,11 @@
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M177" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6502,10 +6683,11 @@
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
-      <c r="K178" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M178" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6536,10 +6718,11 @@
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
-      <c r="K179" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M179" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6570,10 +6753,11 @@
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
-      <c r="K180" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K180" t="inlineStr"/>
       <c r="L180" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M180" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6604,10 +6788,11 @@
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
-      <c r="K181" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M181" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6638,10 +6823,11 @@
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M182" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6672,10 +6858,11 @@
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
-      <c r="K183" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M183" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6706,10 +6893,11 @@
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
-      <c r="K184" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M184" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6740,10 +6928,11 @@
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
-      <c r="K185" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K185" t="inlineStr"/>
       <c r="L185" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M185" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6774,10 +6963,11 @@
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
-      <c r="K186" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K186" t="inlineStr"/>
       <c r="L186" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M186" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6808,10 +6998,11 @@
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr"/>
-      <c r="K187" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M187" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6842,10 +7033,11 @@
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
-      <c r="K188" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M188" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6876,10 +7068,11 @@
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
-      <c r="K189" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M189" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6910,10 +7103,11 @@
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr"/>
-      <c r="K190" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M190" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6944,10 +7138,11 @@
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
-      <c r="K191" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M191" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -6978,10 +7173,11 @@
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
-      <c r="K192" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M192" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7012,10 +7208,11 @@
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
-      <c r="K193" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M193" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7046,10 +7243,11 @@
       </c>
       <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
-      <c r="K194" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M194" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7080,10 +7278,11 @@
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
-      <c r="K195" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M195" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7114,10 +7313,11 @@
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
-      <c r="K196" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M196" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7148,10 +7348,11 @@
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
-      <c r="K197" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M197" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7182,10 +7383,11 @@
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
-      <c r="K198" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M198" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7216,10 +7418,11 @@
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr"/>
-      <c r="K199" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K199" t="inlineStr"/>
       <c r="L199" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M199" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7250,10 +7453,11 @@
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M200" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7284,10 +7488,11 @@
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr"/>
-      <c r="K201" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M201" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7318,10 +7523,11 @@
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
-      <c r="K202" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M202" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7352,10 +7558,11 @@
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr"/>
-      <c r="K203" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M203" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7386,10 +7593,11 @@
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M204" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7420,10 +7628,11 @@
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr"/>
-      <c r="K205" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M205" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7454,10 +7663,11 @@
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr"/>
-      <c r="K206" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M206" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7488,10 +7698,11 @@
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr"/>
-      <c r="K207" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M207" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7522,10 +7733,11 @@
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr"/>
-      <c r="K208" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M208" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7556,10 +7768,11 @@
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
-      <c r="K209" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M209" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7590,10 +7803,11 @@
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
-      <c r="K210" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M210" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7624,10 +7838,11 @@
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr"/>
-      <c r="K211" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K211" t="inlineStr"/>
       <c r="L211" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M211" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7658,10 +7873,11 @@
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr"/>
-      <c r="K212" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M212" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7692,10 +7908,11 @@
       </c>
       <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr"/>
-      <c r="K213" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M213" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7726,10 +7943,11 @@
       </c>
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr"/>
-      <c r="K214" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M214" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7760,10 +7978,11 @@
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
-      <c r="K215" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K215" t="inlineStr"/>
       <c r="L215" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M215" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7794,10 +8013,11 @@
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
-      <c r="K216" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K216" t="inlineStr"/>
       <c r="L216" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M216" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7828,10 +8048,11 @@
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
-      <c r="K217" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K217" t="inlineStr"/>
       <c r="L217" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M217" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7862,10 +8083,11 @@
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr"/>
-      <c r="K218" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M218" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7896,10 +8118,11 @@
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr"/>
-      <c r="K219" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M219" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7930,10 +8153,11 @@
       </c>
       <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr"/>
-      <c r="K220" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M220" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7964,10 +8188,11 @@
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr"/>
-      <c r="K221" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K221" t="inlineStr"/>
       <c r="L221" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M221" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -7998,10 +8223,11 @@
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr"/>
-      <c r="K222" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K222" t="inlineStr"/>
       <c r="L222" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M222" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8032,10 +8258,11 @@
       </c>
       <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr"/>
-      <c r="K223" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K223" t="inlineStr"/>
       <c r="L223" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M223" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8066,10 +8293,11 @@
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
-      <c r="K224" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K224" t="inlineStr"/>
       <c r="L224" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M224" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8100,10 +8328,11 @@
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M225" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8134,10 +8363,11 @@
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr"/>
-      <c r="K226" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M226" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8168,10 +8398,11 @@
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr"/>
-      <c r="K227" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K227" t="inlineStr"/>
       <c r="L227" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M227" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8202,10 +8433,11 @@
       </c>
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr"/>
-      <c r="K228" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K228" t="inlineStr"/>
       <c r="L228" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M228" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8236,10 +8468,11 @@
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr"/>
-      <c r="K229" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K229" t="inlineStr"/>
       <c r="L229" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M229" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8270,10 +8503,11 @@
       </c>
       <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr"/>
-      <c r="K230" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M230" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8304,10 +8538,11 @@
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr"/>
-      <c r="K231" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K231" t="inlineStr"/>
       <c r="L231" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M231" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8338,10 +8573,11 @@
       </c>
       <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr"/>
-      <c r="K232" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K232" t="inlineStr"/>
       <c r="L232" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M232" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8372,10 +8608,11 @@
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr"/>
-      <c r="K233" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K233" t="inlineStr"/>
       <c r="L233" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M233" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8406,10 +8643,11 @@
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
-      <c r="K234" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K234" t="inlineStr"/>
       <c r="L234" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M234" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8440,10 +8678,11 @@
       </c>
       <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr"/>
-      <c r="K235" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K235" t="inlineStr"/>
       <c r="L235" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M235" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8474,10 +8713,11 @@
       </c>
       <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr"/>
-      <c r="K236" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K236" t="inlineStr"/>
       <c r="L236" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M236" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8508,10 +8748,11 @@
       </c>
       <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr"/>
-      <c r="K237" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K237" t="inlineStr"/>
       <c r="L237" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M237" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8542,10 +8783,11 @@
       </c>
       <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr"/>
-      <c r="K238" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K238" t="inlineStr"/>
       <c r="L238" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M238" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8576,10 +8818,11 @@
       </c>
       <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr"/>
-      <c r="K239" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K239" t="inlineStr"/>
       <c r="L239" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M239" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8610,10 +8853,11 @@
       </c>
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr"/>
-      <c r="K240" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K240" t="inlineStr"/>
       <c r="L240" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M240" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8644,10 +8888,11 @@
       </c>
       <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr"/>
-      <c r="K241" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K241" t="inlineStr"/>
       <c r="L241" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M241" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8678,10 +8923,11 @@
       </c>
       <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr"/>
-      <c r="K242" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K242" t="inlineStr"/>
       <c r="L242" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M242" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8712,10 +8958,11 @@
       </c>
       <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr"/>
-      <c r="K243" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K243" t="inlineStr"/>
       <c r="L243" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M243" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8746,10 +8993,11 @@
       </c>
       <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr"/>
-      <c r="K244" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K244" t="inlineStr"/>
       <c r="L244" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M244" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8780,10 +9028,11 @@
       </c>
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
-      <c r="K245" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K245" t="inlineStr"/>
       <c r="L245" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M245" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8814,10 +9063,11 @@
       </c>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
-      <c r="K246" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K246" t="inlineStr"/>
       <c r="L246" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M246" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8848,10 +9098,11 @@
       </c>
       <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr"/>
-      <c r="K247" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K247" t="inlineStr"/>
       <c r="L247" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M247" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8882,10 +9133,11 @@
       </c>
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr"/>
-      <c r="K248" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M248" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8916,10 +9168,11 @@
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
-      <c r="K249" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K249" t="inlineStr"/>
       <c r="L249" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M249" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8950,10 +9203,11 @@
       </c>
       <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr"/>
-      <c r="K250" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K250" t="inlineStr"/>
       <c r="L250" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M250" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -8984,10 +9238,11 @@
       </c>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
-      <c r="K251" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K251" t="inlineStr"/>
       <c r="L251" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M251" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9018,10 +9273,11 @@
       </c>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
-      <c r="K252" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K252" t="inlineStr"/>
       <c r="L252" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M252" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9052,10 +9308,11 @@
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
-      <c r="K253" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K253" t="inlineStr"/>
       <c r="L253" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M253" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9086,10 +9343,11 @@
       </c>
       <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr"/>
-      <c r="K254" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K254" t="inlineStr"/>
       <c r="L254" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M254" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9120,10 +9378,11 @@
       </c>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
-      <c r="K255" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M255" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9154,10 +9413,11 @@
       </c>
       <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr"/>
-      <c r="K256" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K256" t="inlineStr"/>
       <c r="L256" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M256" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9188,10 +9448,11 @@
       </c>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
-      <c r="K257" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K257" t="inlineStr"/>
       <c r="L257" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M257" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9222,10 +9483,11 @@
       </c>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
-      <c r="K258" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M258" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9256,10 +9518,11 @@
       </c>
       <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr"/>
-      <c r="K259" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K259" t="inlineStr"/>
       <c r="L259" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M259" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9290,10 +9553,11 @@
       </c>
       <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr"/>
-      <c r="K260" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K260" t="inlineStr"/>
       <c r="L260" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M260" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9324,10 +9588,11 @@
       </c>
       <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr"/>
-      <c r="K261" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M261" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9358,10 +9623,11 @@
       </c>
       <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr"/>
-      <c r="K262" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K262" t="inlineStr"/>
       <c r="L262" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M262" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9392,10 +9658,11 @@
       </c>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
-      <c r="K263" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K263" t="inlineStr"/>
       <c r="L263" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M263" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9426,10 +9693,11 @@
       </c>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
-      <c r="K264" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M264" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9460,10 +9728,11 @@
       </c>
       <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr"/>
-      <c r="K265" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K265" t="inlineStr"/>
       <c r="L265" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M265" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9494,10 +9763,11 @@
       </c>
       <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr"/>
-      <c r="K266" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K266" t="inlineStr"/>
       <c r="L266" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M266" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9528,10 +9798,11 @@
       </c>
       <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr"/>
-      <c r="K267" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K267" t="inlineStr"/>
       <c r="L267" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M267" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9562,10 +9833,11 @@
       </c>
       <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr"/>
-      <c r="K268" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K268" t="inlineStr"/>
       <c r="L268" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M268" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9596,10 +9868,11 @@
       </c>
       <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr"/>
-      <c r="K269" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M269" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9630,10 +9903,11 @@
       </c>
       <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr"/>
-      <c r="K270" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K270" t="inlineStr"/>
       <c r="L270" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M270" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9664,10 +9938,11 @@
       </c>
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr"/>
-      <c r="K271" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K271" t="inlineStr"/>
       <c r="L271" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M271" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9698,10 +9973,11 @@
       </c>
       <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr"/>
-      <c r="K272" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K272" t="inlineStr"/>
       <c r="L272" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M272" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9732,10 +10008,11 @@
       </c>
       <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr"/>
-      <c r="K273" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K273" t="inlineStr"/>
       <c r="L273" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M273" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9766,10 +10043,11 @@
       </c>
       <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr"/>
-      <c r="K274" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K274" t="inlineStr"/>
       <c r="L274" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M274" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9800,10 +10078,11 @@
       </c>
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr"/>
-      <c r="K275" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K275" t="inlineStr"/>
       <c r="L275" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M275" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9834,10 +10113,11 @@
       </c>
       <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr"/>
-      <c r="K276" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K276" t="inlineStr"/>
       <c r="L276" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M276" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9868,10 +10148,11 @@
       </c>
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr"/>
-      <c r="K277" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K277" t="inlineStr"/>
       <c r="L277" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M277" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9902,10 +10183,11 @@
       </c>
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr"/>
-      <c r="K278" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K278" t="inlineStr"/>
       <c r="L278" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M278" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9936,10 +10218,11 @@
       </c>
       <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr"/>
-      <c r="K279" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K279" t="inlineStr"/>
       <c r="L279" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M279" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -9970,10 +10253,11 @@
       </c>
       <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr"/>
-      <c r="K280" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K280" t="inlineStr"/>
       <c r="L280" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M280" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10004,10 +10288,11 @@
       </c>
       <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr"/>
-      <c r="K281" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K281" t="inlineStr"/>
       <c r="L281" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M281" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10038,10 +10323,11 @@
       </c>
       <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr"/>
-      <c r="K282" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K282" t="inlineStr"/>
       <c r="L282" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M282" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10072,10 +10358,11 @@
       </c>
       <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr"/>
-      <c r="K283" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K283" t="inlineStr"/>
       <c r="L283" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M283" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10106,10 +10393,11 @@
       </c>
       <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr"/>
-      <c r="K284" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K284" t="inlineStr"/>
       <c r="L284" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M284" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10140,10 +10428,11 @@
       </c>
       <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr"/>
-      <c r="K285" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K285" t="inlineStr"/>
       <c r="L285" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M285" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10174,10 +10463,11 @@
       </c>
       <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr"/>
-      <c r="K286" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K286" t="inlineStr"/>
       <c r="L286" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M286" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10208,10 +10498,11 @@
       </c>
       <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr"/>
-      <c r="K287" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K287" t="inlineStr"/>
       <c r="L287" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M287" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10242,10 +10533,11 @@
       </c>
       <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr"/>
-      <c r="K288" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K288" t="inlineStr"/>
       <c r="L288" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M288" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10276,10 +10568,11 @@
       </c>
       <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr"/>
-      <c r="K289" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K289" t="inlineStr"/>
       <c r="L289" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M289" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10310,10 +10603,11 @@
       </c>
       <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr"/>
-      <c r="K290" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K290" t="inlineStr"/>
       <c r="L290" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M290" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10344,10 +10638,11 @@
       </c>
       <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr"/>
-      <c r="K291" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K291" t="inlineStr"/>
       <c r="L291" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M291" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10378,10 +10673,11 @@
       </c>
       <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr"/>
-      <c r="K292" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K292" t="inlineStr"/>
       <c r="L292" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M292" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10412,10 +10708,11 @@
       </c>
       <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr"/>
-      <c r="K293" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K293" t="inlineStr"/>
       <c r="L293" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M293" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10446,10 +10743,11 @@
       </c>
       <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr"/>
-      <c r="K294" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K294" t="inlineStr"/>
       <c r="L294" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M294" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10480,10 +10778,11 @@
       </c>
       <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr"/>
-      <c r="K295" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K295" t="inlineStr"/>
       <c r="L295" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M295" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10514,10 +10813,11 @@
       </c>
       <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr"/>
-      <c r="K296" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K296" t="inlineStr"/>
       <c r="L296" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M296" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10548,10 +10848,11 @@
       </c>
       <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr"/>
-      <c r="K297" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K297" t="inlineStr"/>
       <c r="L297" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M297" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10582,10 +10883,11 @@
       </c>
       <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr"/>
-      <c r="K298" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K298" t="inlineStr"/>
       <c r="L298" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M298" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10616,10 +10918,11 @@
       </c>
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
-      <c r="K299" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K299" t="inlineStr"/>
       <c r="L299" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M299" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10650,10 +10953,11 @@
       </c>
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr"/>
-      <c r="K300" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K300" t="inlineStr"/>
       <c r="L300" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M300" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10684,10 +10988,11 @@
       </c>
       <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr"/>
-      <c r="K301" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K301" t="inlineStr"/>
       <c r="L301" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M301" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10718,10 +11023,11 @@
       </c>
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr"/>
-      <c r="K302" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K302" t="inlineStr"/>
       <c r="L302" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M302" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10752,10 +11058,11 @@
       </c>
       <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr"/>
-      <c r="K303" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K303" t="inlineStr"/>
       <c r="L303" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M303" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10786,10 +11093,11 @@
       </c>
       <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr"/>
-      <c r="K304" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K304" t="inlineStr"/>
       <c r="L304" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M304" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10820,10 +11128,11 @@
       </c>
       <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr"/>
-      <c r="K305" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K305" t="inlineStr"/>
       <c r="L305" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M305" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10854,10 +11163,11 @@
       </c>
       <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr"/>
-      <c r="K306" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K306" t="inlineStr"/>
       <c r="L306" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M306" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10888,10 +11198,11 @@
       </c>
       <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr"/>
-      <c r="K307" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K307" t="inlineStr"/>
       <c r="L307" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M307" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10922,10 +11233,11 @@
       </c>
       <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
-      <c r="K308" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K308" t="inlineStr"/>
       <c r="L308" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M308" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10956,10 +11268,11 @@
       </c>
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr"/>
-      <c r="K309" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K309" t="inlineStr"/>
       <c r="L309" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M309" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -10990,10 +11303,11 @@
       </c>
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr"/>
-      <c r="K310" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K310" t="inlineStr"/>
       <c r="L310" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M310" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11024,10 +11338,11 @@
       </c>
       <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr"/>
-      <c r="K311" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K311" t="inlineStr"/>
       <c r="L311" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M311" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11058,10 +11373,11 @@
       </c>
       <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr"/>
-      <c r="K312" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K312" t="inlineStr"/>
       <c r="L312" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M312" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11092,10 +11408,11 @@
       </c>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
-      <c r="K313" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K313" t="inlineStr"/>
       <c r="L313" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M313" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11126,10 +11443,11 @@
       </c>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
-      <c r="K314" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K314" t="inlineStr"/>
       <c r="L314" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M314" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11160,10 +11478,11 @@
       </c>
       <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr"/>
-      <c r="K315" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K315" t="inlineStr"/>
       <c r="L315" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M315" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11194,10 +11513,11 @@
       </c>
       <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr"/>
-      <c r="K316" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K316" t="inlineStr"/>
       <c r="L316" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M316" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11228,10 +11548,11 @@
       </c>
       <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr"/>
-      <c r="K317" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K317" t="inlineStr"/>
       <c r="L317" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M317" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11262,10 +11583,11 @@
       </c>
       <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr"/>
-      <c r="K318" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K318" t="inlineStr"/>
       <c r="L318" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M318" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11296,10 +11618,11 @@
       </c>
       <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr"/>
-      <c r="K319" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K319" t="inlineStr"/>
       <c r="L319" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M319" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11330,10 +11653,11 @@
       </c>
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
-      <c r="K320" t="n">
-        <v>116.4121952</v>
-      </c>
+      <c r="K320" t="inlineStr"/>
       <c r="L320" t="n">
+        <v>116.4121952</v>
+      </c>
+      <c r="M320" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11364,10 +11688,11 @@
       </c>
       <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr"/>
-      <c r="K321" t="n">
+      <c r="K321" t="inlineStr"/>
+      <c r="L321" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L321" t="n">
+      <c r="M321" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11398,10 +11723,11 @@
       </c>
       <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr"/>
-      <c r="K322" t="n">
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L322" t="n">
+      <c r="M322" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11432,10 +11758,11 @@
       </c>
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
-      <c r="K323" t="n">
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L323" t="n">
+      <c r="M323" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11466,10 +11793,11 @@
       </c>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
-      <c r="K324" t="n">
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L324" t="n">
+      <c r="M324" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11500,10 +11828,11 @@
       </c>
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr"/>
-      <c r="K325" t="n">
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L325" t="n">
+      <c r="M325" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11534,10 +11863,11 @@
       </c>
       <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr"/>
-      <c r="K326" t="n">
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L326" t="n">
+      <c r="M326" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11568,10 +11898,11 @@
       </c>
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr"/>
-      <c r="K327" t="n">
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L327" t="n">
+      <c r="M327" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11602,10 +11933,11 @@
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr"/>
-      <c r="K328" t="n">
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L328" t="n">
+      <c r="M328" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11636,10 +11968,11 @@
       </c>
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
-      <c r="K329" t="n">
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L329" t="n">
+      <c r="M329" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11670,10 +12003,11 @@
       </c>
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
-      <c r="K330" t="n">
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L330" t="n">
+      <c r="M330" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11704,10 +12038,11 @@
       </c>
       <c r="I331" t="inlineStr"/>
       <c r="J331" t="inlineStr"/>
-      <c r="K331" t="n">
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L331" t="n">
+      <c r="M331" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11738,10 +12073,11 @@
       </c>
       <c r="I332" t="inlineStr"/>
       <c r="J332" t="inlineStr"/>
-      <c r="K332" t="n">
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L332" t="n">
+      <c r="M332" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11772,10 +12108,11 @@
       </c>
       <c r="I333" t="inlineStr"/>
       <c r="J333" t="inlineStr"/>
-      <c r="K333" t="n">
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L333" t="n">
+      <c r="M333" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11806,10 +12143,11 @@
       </c>
       <c r="I334" t="inlineStr"/>
       <c r="J334" t="inlineStr"/>
-      <c r="K334" t="n">
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="n">
         <v>0.0121952</v>
       </c>
-      <c r="L334" t="n">
+      <c r="M334" t="n">
         <v>12792.90181321</v>
       </c>
     </row>
@@ -11842,6 +12180,7 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="n">
@@ -11872,6 +12211,7 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="n">
@@ -11902,6 +12242,7 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="n">
@@ -11932,6 +12273,7 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="n">
@@ -11962,6 +12304,7 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="n">
@@ -11992,6 +12335,7 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="n">
@@ -12022,6 +12366,7 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="n">
@@ -12052,6 +12397,7 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr"/>
+      <c r="M342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="n">
@@ -12082,6 +12428,7 @@
       <c r="J343" t="inlineStr"/>
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="n">
@@ -12114,6 +12461,7 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="n">
@@ -12146,6 +12494,7 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr"/>
+      <c r="M345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="n">
@@ -12178,6 +12527,7 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="n">
@@ -12210,6 +12560,7 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="n">
@@ -12242,6 +12593,7 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr"/>
+      <c r="M348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="n">
@@ -12274,6 +12626,7 @@
       <c r="J349" t="inlineStr"/>
       <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr"/>
+      <c r="M349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="n">
@@ -12306,6 +12659,7 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="n">
@@ -12338,6 +12692,7 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="n">
@@ -12370,6 +12725,7 @@
       <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="n">
@@ -12402,6 +12758,7 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="n">
@@ -12434,6 +12791,7 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr"/>
+      <c r="M354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="n">
@@ -12466,6 +12824,7 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="n">
@@ -12498,6 +12857,7 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="n">
@@ -12530,6 +12890,7 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="n">
@@ -12562,6 +12923,7 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="n">
@@ -12594,6 +12956,7 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="n">
@@ -12626,6 +12989,7 @@
       <c r="J360" t="inlineStr"/>
       <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="n">
@@ -12658,6 +13022,7 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="n">
@@ -12690,6 +13055,7 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="n">
@@ -12722,6 +13088,7 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="n">
@@ -12754,6 +13121,7 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="n">
@@ -12786,6 +13154,7 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="n">
@@ -12818,6 +13187,7 @@
       <c r="J366" t="inlineStr"/>
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr"/>
+      <c r="M366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="n">
@@ -12850,6 +13220,7 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="n">
@@ -12882,6 +13253,7 @@
       <c r="J368" t="inlineStr"/>
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="n">
@@ -12914,6 +13286,7 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr"/>
+      <c r="M369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="n">
@@ -12946,6 +13319,7 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="n">
@@ -12978,6 +13352,7 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="n">
@@ -13010,6 +13385,7 @@
       <c r="J372" t="inlineStr"/>
       <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr"/>
+      <c r="M372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="n">
@@ -13042,6 +13418,7 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr"/>
       <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="n">
@@ -13074,6 +13451,7 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="n">
@@ -13106,6 +13484,7 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="n">
@@ -13138,6 +13517,7 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="n">
@@ -13170,6 +13550,7 @@
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="n">
@@ -13202,6 +13583,7 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="n">
@@ -13234,6 +13616,7 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="n">
@@ -13266,6 +13649,7 @@
       <c r="J380" t="inlineStr"/>
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="n">
@@ -13298,6 +13682,7 @@
       <c r="J381" t="inlineStr"/>
       <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="n">
@@ -13330,6 +13715,7 @@
       <c r="J382" t="inlineStr"/>
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="n">
@@ -13362,6 +13748,7 @@
       <c r="J383" t="inlineStr"/>
       <c r="K383" t="inlineStr"/>
       <c r="L383" t="inlineStr"/>
+      <c r="M383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="n">
@@ -13394,6 +13781,7 @@
       <c r="J384" t="inlineStr"/>
       <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="n">
@@ -13426,6 +13814,7 @@
       <c r="J385" t="inlineStr"/>
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="n">
@@ -13458,6 +13847,7 @@
       <c r="J386" t="inlineStr"/>
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="n">
@@ -13490,6 +13880,7 @@
       <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
+      <c r="M387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="n">
@@ -13522,6 +13913,7 @@
       <c r="J388" t="inlineStr"/>
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="n">
@@ -13554,6 +13946,7 @@
       <c r="J389" t="inlineStr"/>
       <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="n">
@@ -13586,6 +13979,7 @@
       <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr"/>
+      <c r="M390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="n">
@@ -13618,6 +14012,7 @@
       <c r="J391" t="inlineStr"/>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="n">
@@ -13650,6 +14045,7 @@
       <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr"/>
       <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="n">
@@ -13682,6 +14078,7 @@
       <c r="J393" t="inlineStr"/>
       <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="n">
@@ -13714,6 +14111,7 @@
       <c r="J394" t="inlineStr"/>
       <c r="K394" t="inlineStr"/>
       <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="n">
@@ -13746,6 +14144,7 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="n">
@@ -13778,6 +14177,7 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="n">
@@ -13810,6 +14210,7 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="n">
@@ -13842,6 +14243,7 @@
       <c r="J398" t="inlineStr"/>
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="n">
@@ -13874,6 +14276,7 @@
       <c r="J399" t="inlineStr"/>
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="n">
@@ -13906,6 +14309,7 @@
       <c r="J400" t="inlineStr"/>
       <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="n">
@@ -13938,6 +14342,7 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="n">
@@ -13970,6 +14375,7 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="n">
@@ -14002,6 +14408,7 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="n">
@@ -14034,6 +14441,7 @@
       <c r="J404" t="inlineStr"/>
       <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="n">
@@ -14066,6 +14474,7 @@
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr"/>
+      <c r="M405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="n">
@@ -14098,6 +14507,7 @@
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr"/>
+      <c r="M406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="n">
@@ -14130,6 +14540,7 @@
       <c r="J407" t="inlineStr"/>
       <c r="K407" t="inlineStr"/>
       <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="n">
@@ -14162,6 +14573,7 @@
       <c r="J408" t="inlineStr"/>
       <c r="K408" t="inlineStr"/>
       <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="n">
@@ -14194,6 +14606,7 @@
       <c r="J409" t="inlineStr"/>
       <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="n">
@@ -14226,6 +14639,7 @@
       <c r="J410" t="inlineStr"/>
       <c r="K410" t="inlineStr"/>
       <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="n">
@@ -14258,6 +14672,7 @@
       <c r="J411" t="inlineStr"/>
       <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr"/>
+      <c r="M411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="n">
@@ -14290,6 +14705,7 @@
       <c r="J412" t="inlineStr"/>
       <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="n">
@@ -14322,6 +14738,7 @@
       <c r="J413" t="inlineStr"/>
       <c r="K413" t="inlineStr"/>
       <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="n">
@@ -14354,6 +14771,7 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="n">
@@ -14386,6 +14804,7 @@
       <c r="J415" t="inlineStr"/>
       <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="n">
@@ -14418,6 +14837,7 @@
       <c r="J416" t="inlineStr"/>
       <c r="K416" t="inlineStr"/>
       <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="n">
@@ -14450,6 +14870,7 @@
       <c r="J417" t="inlineStr"/>
       <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="n">
@@ -14482,6 +14903,7 @@
       <c r="J418" t="inlineStr"/>
       <c r="K418" t="inlineStr"/>
       <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="n">
@@ -14514,6 +14936,7 @@
       <c r="J419" t="inlineStr"/>
       <c r="K419" t="inlineStr"/>
       <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="n">
@@ -14546,6 +14969,7 @@
       <c r="J420" t="inlineStr"/>
       <c r="K420" t="inlineStr"/>
       <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="n">
@@ -14578,6 +15002,7 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr"/>
+      <c r="M421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="n">
@@ -14610,6 +15035,7 @@
       <c r="J422" t="inlineStr"/>
       <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="n">
@@ -14642,6 +15068,7 @@
       <c r="J423" t="inlineStr"/>
       <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr"/>
+      <c r="M423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="n">
@@ -14674,6 +15101,7 @@
       <c r="J424" t="inlineStr"/>
       <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="n">
@@ -14706,6 +15134,7 @@
       <c r="J425" t="inlineStr"/>
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr"/>
+      <c r="M425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="n">
@@ -14738,6 +15167,7 @@
       <c r="J426" t="inlineStr"/>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr"/>
+      <c r="M426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="n">
@@ -14770,6 +15200,7 @@
       <c r="J427" t="inlineStr"/>
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="n">
@@ -14802,6 +15233,7 @@
       <c r="J428" t="inlineStr"/>
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="n">
@@ -14834,6 +15266,7 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="n">
@@ -14866,6 +15299,7 @@
       <c r="J430" t="inlineStr"/>
       <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="n">
@@ -14898,6 +15332,7 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr"/>
       <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="n">
@@ -14930,6 +15365,7 @@
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr"/>
       <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="n">
@@ -14962,6 +15398,7 @@
       <c r="J433" t="inlineStr"/>
       <c r="K433" t="inlineStr"/>
       <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="n">
@@ -14991,11 +15428,12 @@
       <c r="I434" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J434" t="n">
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="n">
         <v>0.048</v>
       </c>
-      <c r="K434" t="inlineStr"/>
       <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="n">
@@ -15025,11 +15463,12 @@
       <c r="I435" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J435" t="n">
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="n">
         <v>0.048</v>
       </c>
-      <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="n">
@@ -15059,11 +15498,12 @@
       <c r="I436" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J436" t="n">
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="n">
         <v>0.048</v>
       </c>
-      <c r="K436" t="inlineStr"/>
       <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="n">
@@ -15093,11 +15533,12 @@
       <c r="I437" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J437" t="n">
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="n">
         <v>0.048</v>
       </c>
-      <c r="K437" t="inlineStr"/>
       <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="n">
@@ -15127,11 +15568,12 @@
       <c r="I438" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J438" t="n">
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="n">
         <v>0.048</v>
       </c>
-      <c r="K438" t="inlineStr"/>
       <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="n">
@@ -15161,11 +15603,12 @@
       <c r="I439" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J439" t="n">
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="n">
         <v>0.048</v>
       </c>
-      <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="n">
@@ -15195,11 +15638,12 @@
       <c r="I440" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J440" t="n">
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="n">
         <v>0.048</v>
       </c>
-      <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="n">
@@ -15229,11 +15673,12 @@
       <c r="I441" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J441" t="n">
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="n">
         <v>0.048</v>
       </c>
-      <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="n">
@@ -15263,11 +15708,12 @@
       <c r="I442" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J442" t="n">
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="n">
         <v>0.048</v>
       </c>
-      <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="n">
@@ -15297,11 +15743,12 @@
       <c r="I443" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J443" t="n">
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="n">
         <v>0.048</v>
       </c>
-      <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="n">
@@ -15331,11 +15778,12 @@
       <c r="I444" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J444" t="n">
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="n">
         <v>0.048</v>
       </c>
-      <c r="K444" t="inlineStr"/>
       <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="n">
@@ -15365,11 +15813,12 @@
       <c r="I445" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J445" t="n">
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="n">
         <v>0.048</v>
       </c>
-      <c r="K445" t="inlineStr"/>
       <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="n">
@@ -15399,11 +15848,12 @@
       <c r="I446" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J446" t="n">
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="n">
         <v>0.048</v>
       </c>
-      <c r="K446" t="inlineStr"/>
       <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="n">
@@ -15433,11 +15883,12 @@
       <c r="I447" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J447" t="n">
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="n">
         <v>0.048</v>
       </c>
-      <c r="K447" t="inlineStr"/>
       <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="n">
@@ -15467,11 +15918,12 @@
       <c r="I448" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J448" t="n">
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="n">
         <v>0.048</v>
       </c>
-      <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="n">
@@ -15501,11 +15953,12 @@
       <c r="I449" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J449" t="n">
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="n">
         <v>0.048</v>
       </c>
-      <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="n">
@@ -15535,11 +15988,12 @@
       <c r="I450" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J450" t="n">
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="n">
         <v>0.048</v>
       </c>
-      <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="n">
@@ -15569,11 +16023,12 @@
       <c r="I451" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J451" t="n">
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="n">
         <v>0.048</v>
       </c>
-      <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="n">
@@ -15603,11 +16058,12 @@
       <c r="I452" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J452" t="n">
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="n">
         <v>0.048</v>
       </c>
-      <c r="K452" t="inlineStr"/>
       <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="n">
@@ -15637,11 +16093,12 @@
       <c r="I453" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J453" t="n">
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="n">
         <v>0.048</v>
       </c>
-      <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="n">
@@ -15671,11 +16128,12 @@
       <c r="I454" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J454" t="n">
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="n">
         <v>0.048</v>
       </c>
-      <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="n">
@@ -15705,11 +16163,12 @@
       <c r="I455" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J455" t="n">
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="n">
         <v>0.048</v>
       </c>
-      <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="n">
@@ -15739,11 +16198,12 @@
       <c r="I456" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J456" t="n">
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="n">
         <v>0.048</v>
       </c>
-      <c r="K456" t="inlineStr"/>
       <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="n">
@@ -15773,11 +16233,12 @@
       <c r="I457" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J457" t="n">
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="n">
         <v>0.048</v>
       </c>
-      <c r="K457" t="inlineStr"/>
       <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="n">
@@ -15807,11 +16268,12 @@
       <c r="I458" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J458" t="n">
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="n">
         <v>0.048</v>
       </c>
-      <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="n">
@@ -15841,11 +16303,12 @@
       <c r="I459" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J459" t="n">
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="n">
         <v>0.048</v>
       </c>
-      <c r="K459" t="inlineStr"/>
       <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="n">
@@ -15875,11 +16338,12 @@
       <c r="I460" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J460" t="n">
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="n">
         <v>0.048</v>
       </c>
-      <c r="K460" t="inlineStr"/>
       <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="n">
@@ -15909,11 +16373,12 @@
       <c r="I461" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J461" t="n">
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="n">
         <v>0.048</v>
       </c>
-      <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="n">
@@ -15943,11 +16408,12 @@
       <c r="I462" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J462" t="n">
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="n">
         <v>0.048</v>
       </c>
-      <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="n">
@@ -15977,11 +16443,12 @@
       <c r="I463" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J463" t="n">
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="n">
         <v>0.048</v>
       </c>
-      <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="n">
@@ -16011,11 +16478,12 @@
       <c r="I464" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J464" t="n">
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="n">
         <v>0.048</v>
       </c>
-      <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="n">
@@ -16045,11 +16513,12 @@
       <c r="I465" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J465" t="n">
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="n">
         <v>0.048</v>
       </c>
-      <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="n">
@@ -16079,11 +16548,12 @@
       <c r="I466" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="J466" t="n">
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="n">
         <v>0.048</v>
       </c>
-      <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="n">
@@ -16116,6 +16586,7 @@
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr"/>
       <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="n">
@@ -16148,6 +16619,7 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr"/>
       <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="n">
@@ -16180,6 +16652,7 @@
       <c r="J469" t="inlineStr"/>
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="n">
@@ -16212,6 +16685,7 @@
       <c r="J470" t="inlineStr"/>
       <c r="K470" t="inlineStr"/>
       <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="n">
@@ -16244,6 +16718,7 @@
       <c r="J471" t="inlineStr"/>
       <c r="K471" t="inlineStr"/>
       <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="n">
@@ -16276,6 +16751,7 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="n">
@@ -16308,6 +16784,7 @@
       <c r="J473" t="inlineStr"/>
       <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="n">
@@ -16340,6 +16817,7 @@
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr"/>
       <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="n">
@@ -16372,6 +16850,7 @@
       <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="n">
@@ -16404,6 +16883,7 @@
       <c r="J476" t="inlineStr"/>
       <c r="K476" t="inlineStr"/>
       <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="n">
@@ -16436,6 +16916,7 @@
       <c r="J477" t="inlineStr"/>
       <c r="K477" t="inlineStr"/>
       <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="n">
@@ -16468,6 +16949,7 @@
       <c r="J478" t="inlineStr"/>
       <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="n">
@@ -16500,6 +16982,7 @@
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="n">
@@ -16532,6 +17015,7 @@
       <c r="J480" t="inlineStr"/>
       <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="n">
@@ -16564,6 +17048,7 @@
       <c r="J481" t="inlineStr"/>
       <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="n">
@@ -16596,6 +17081,7 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="n">
@@ -16628,6 +17114,7 @@
       <c r="J483" t="inlineStr"/>
       <c r="K483" t="inlineStr"/>
       <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="n">
@@ -16660,6 +17147,7 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="n">
@@ -16692,6 +17180,7 @@
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr"/>
       <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="n">
@@ -16724,6 +17213,7 @@
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr"/>
       <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="n">
@@ -16756,6 +17246,7 @@
       <c r="J487" t="inlineStr"/>
       <c r="K487" t="inlineStr"/>
       <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="n">
@@ -16788,6 +17279,7 @@
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr"/>
       <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="n">
@@ -16820,6 +17312,7 @@
       <c r="J489" t="inlineStr"/>
       <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="n">
@@ -16852,6 +17345,7 @@
       <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="n">
@@ -16884,6 +17378,7 @@
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="n">
@@ -16916,6 +17411,7 @@
       <c r="J492" t="inlineStr"/>
       <c r="K492" t="inlineStr"/>
       <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="n">
@@ -16948,6 +17444,7 @@
       <c r="J493" t="inlineStr"/>
       <c r="K493" t="inlineStr"/>
       <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="n">
@@ -16980,6 +17477,7 @@
       <c r="J494" t="inlineStr"/>
       <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="n">
@@ -17012,6 +17510,7 @@
       <c r="J495" t="inlineStr"/>
       <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="n">
@@ -17044,6 +17543,7 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="n">
@@ -17076,6 +17576,7 @@
       <c r="J497" t="inlineStr"/>
       <c r="K497" t="inlineStr"/>
       <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="n">
@@ -17108,6 +17609,7 @@
       <c r="J498" t="inlineStr"/>
       <c r="K498" t="inlineStr"/>
       <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="n">
@@ -17140,6 +17642,7 @@
       <c r="J499" t="inlineStr"/>
       <c r="K499" t="inlineStr"/>
       <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="n">
@@ -17172,6 +17675,7 @@
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="n">
@@ -17204,6 +17708,7 @@
       <c r="J501" t="inlineStr"/>
       <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="n">
@@ -17236,6 +17741,7 @@
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="n">
@@ -17268,6 +17774,7 @@
       <c r="J503" t="inlineStr"/>
       <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
@@ -17300,6 +17807,7 @@
       <c r="J504" t="inlineStr"/>
       <c r="K504" t="inlineStr"/>
       <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
@@ -17332,6 +17840,7 @@
       <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
@@ -17364,6 +17873,7 @@
       <c r="J506" t="inlineStr"/>
       <c r="K506" t="inlineStr"/>
       <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
@@ -17396,6 +17906,7 @@
       <c r="J507" t="inlineStr"/>
       <c r="K507" t="inlineStr"/>
       <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="n">
@@ -17428,6 +17939,7 @@
       <c r="J508" t="inlineStr"/>
       <c r="K508" t="inlineStr"/>
       <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="n">
@@ -17460,6 +17972,7 @@
       <c r="J509" t="inlineStr"/>
       <c r="K509" t="inlineStr"/>
       <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="n">
@@ -17492,6 +18005,7 @@
       <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="n">
@@ -17524,6 +18038,7 @@
       <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="n">
@@ -17556,6 +18071,7 @@
       <c r="J512" t="inlineStr"/>
       <c r="K512" t="inlineStr"/>
       <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="n">
@@ -17588,6 +18104,7 @@
       <c r="J513" t="inlineStr"/>
       <c r="K513" t="inlineStr"/>
       <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="n">
@@ -17620,6 +18137,7 @@
       <c r="J514" t="inlineStr"/>
       <c r="K514" t="inlineStr"/>
       <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="n">
@@ -17652,6 +18170,7 @@
       <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr"/>
       <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="n">
@@ -17684,6 +18203,7 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="n">
@@ -17716,6 +18236,7 @@
       <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="n">
@@ -17748,6 +18269,7 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="n">
@@ -17780,6 +18302,7 @@
       <c r="J519" t="inlineStr"/>
       <c r="K519" t="inlineStr"/>
       <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="n">
@@ -17812,6 +18335,7 @@
       <c r="J520" t="inlineStr"/>
       <c r="K520" t="inlineStr"/>
       <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="n">
@@ -17844,6 +18368,7 @@
       <c r="J521" t="inlineStr"/>
       <c r="K521" t="inlineStr"/>
       <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="n">
@@ -17876,6 +18401,7 @@
       <c r="J522" t="inlineStr"/>
       <c r="K522" t="inlineStr"/>
       <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="n">
@@ -17908,6 +18434,7 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="n">
@@ -17940,6 +18467,7 @@
       <c r="J524" t="inlineStr"/>
       <c r="K524" t="inlineStr"/>
       <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="n">
@@ -17972,6 +18500,7 @@
       <c r="J525" t="inlineStr"/>
       <c r="K525" t="inlineStr"/>
       <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="n">
@@ -18004,6 +18533,7 @@
       <c r="J526" t="inlineStr"/>
       <c r="K526" t="inlineStr"/>
       <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="n">
@@ -18036,6 +18566,7 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr"/>
       <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="n">
@@ -18066,6 +18597,73 @@
       <c r="J528" t="inlineStr"/>
       <c r="K528" t="inlineStr"/>
       <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B529" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C529" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D529" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E529" t="inlineStr"/>
+      <c r="F529" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G529" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H529" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I529" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J529" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B530" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C530" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D530" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E530" t="inlineStr"/>
+      <c r="F530" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G530" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H530" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I530" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J530" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD1F9D6-56B3-4809-BC0F-329808218427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5437CDCE-6977-4A7E-B4D5-ECDF53A26201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -119,7 +119,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -426,6 +426,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M530"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niroo\Desktop\Jupyter\Projets\Risk Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5437CDCE-6977-4A7E-B4D5-ECDF53A26201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDFBD5B-0F43-4D01-90C0-59302D6391CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>BNBUSDT</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>JASMYUSDT</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
@@ -431,6 +434,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M530"/>
+  <dimension ref="A1:M531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18665,6 +18665,39 @@
       <c r="L530" t="inlineStr"/>
       <c r="M530" t="inlineStr"/>
     </row>
+    <row r="531">
+      <c r="A531" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B531" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C531" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D531" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G531" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H531" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I531" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J531" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M531"/>
+  <dimension ref="A1:M535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18698,6 +18698,138 @@
       <c r="L531" t="inlineStr"/>
       <c r="M531" t="inlineStr"/>
     </row>
+    <row r="532">
+      <c r="A532" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B532" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C532" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D532" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G532" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H532" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I532" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J532" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B533" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C533" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D533" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G533" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H533" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I533" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J533" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B534" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C534" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D534" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G534" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H534" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I534" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J534" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B535" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C535" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D535" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G535" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H535" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I535" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J535" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M535"/>
+  <dimension ref="A1:M536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18830,6 +18830,39 @@
       <c r="L535" t="inlineStr"/>
       <c r="M535" t="inlineStr"/>
     </row>
+    <row r="536">
+      <c r="A536" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B536" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C536" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D536" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G536" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H536" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I536" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J536" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M536"/>
+  <dimension ref="A1:M539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18863,6 +18863,105 @@
       <c r="L536" t="inlineStr"/>
       <c r="M536" t="inlineStr"/>
     </row>
+    <row r="537">
+      <c r="A537" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B537" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C537" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D537" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E537" t="inlineStr"/>
+      <c r="F537" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G537" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H537" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I537" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J537" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B538" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C538" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D538" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G538" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H538" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I538" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J538" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B539" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C539" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D539" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G539" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H539" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I539" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J539" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M539"/>
+  <dimension ref="A1:M541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18962,6 +18962,72 @@
       <c r="L539" t="inlineStr"/>
       <c r="M539" t="inlineStr"/>
     </row>
+    <row r="540">
+      <c r="A540" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B540" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C540" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D540" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G540" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H540" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I540" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J540" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B541" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C541" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D541" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G541" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H541" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I541" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J541" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M541"/>
+  <dimension ref="A1:M544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19028,6 +19028,105 @@
       <c r="L541" t="inlineStr"/>
       <c r="M541" t="inlineStr"/>
     </row>
+    <row r="542">
+      <c r="A542" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B542" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C542" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D542" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E542" t="inlineStr"/>
+      <c r="F542" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G542" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H542" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I542" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J542" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B543" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C543" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D543" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G543" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H543" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I543" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J543" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B544" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C544" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D544" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E544" t="inlineStr"/>
+      <c r="F544" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G544" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H544" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I544" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J544" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M544"/>
+  <dimension ref="A1:M546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19127,6 +19127,72 @@
       <c r="L544" t="inlineStr"/>
       <c r="M544" t="inlineStr"/>
     </row>
+    <row r="545">
+      <c r="A545" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B545" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C545" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D545" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G545" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H545" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I545" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J545" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B546" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C546" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D546" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E546" t="inlineStr"/>
+      <c r="F546" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G546" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H546" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I546" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J546" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M546"/>
+  <dimension ref="A1:M547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19193,6 +19193,39 @@
       <c r="L546" t="inlineStr"/>
       <c r="M546" t="inlineStr"/>
     </row>
+    <row r="547">
+      <c r="A547" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="B547" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C547" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D547" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E547" t="inlineStr"/>
+      <c r="F547" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G547" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H547" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I547" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J547" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M547"/>
+  <dimension ref="A1:M550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19226,6 +19226,105 @@
       <c r="L547" t="inlineStr"/>
       <c r="M547" t="inlineStr"/>
     </row>
+    <row r="548">
+      <c r="A548" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B548" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C548" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D548" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E548" t="inlineStr"/>
+      <c r="F548" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G548" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H548" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I548" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J548" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B549" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C549" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D549" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E549" t="inlineStr"/>
+      <c r="F549" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G549" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H549" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I549" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J549" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B550" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C550" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D550" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E550" t="inlineStr"/>
+      <c r="F550" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G550" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H550" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I550" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J550" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M550"/>
+  <dimension ref="A1:M555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19325,6 +19325,171 @@
       <c r="L550" t="inlineStr"/>
       <c r="M550" t="inlineStr"/>
     </row>
+    <row r="551">
+      <c r="A551" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B551" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C551" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D551" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E551" t="inlineStr"/>
+      <c r="F551" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G551" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H551" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I551" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J551" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B552" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C552" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D552" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E552" t="inlineStr"/>
+      <c r="F552" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G552" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H552" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I552" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J552" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B553" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C553" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D553" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E553" t="inlineStr"/>
+      <c r="F553" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G553" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H553" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I553" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J553" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B554" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C554" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D554" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E554" t="inlineStr"/>
+      <c r="F554" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G554" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H554" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I554" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J554" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B555" t="n">
+        <v>0.00018791</v>
+      </c>
+      <c r="C555" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D555" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E555" t="inlineStr"/>
+      <c r="F555" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G555" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H555" t="n">
+        <v>5691.42185423</v>
+      </c>
+      <c r="I555" t="n">
+        <v>0.008201770000000001</v>
+      </c>
+      <c r="J555" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N557"/>
+  <dimension ref="A1:N560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20119,6 +20119,114 @@
       <c r="M557" t="inlineStr"/>
       <c r="N557" t="inlineStr"/>
     </row>
+    <row r="558">
+      <c r="A558" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B558" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C558" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D558" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E558" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G558" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H558" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I558" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J558" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr"/>
+      <c r="M558" t="inlineStr"/>
+      <c r="N558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B559" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C559" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D559" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E559" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G559" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H559" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I559" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J559" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr"/>
+      <c r="M559" t="inlineStr"/>
+      <c r="N559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B560" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C560" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D560" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E560" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G560" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H560" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I560" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J560" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K560" t="inlineStr"/>
+      <c r="L560" t="inlineStr"/>
+      <c r="M560" t="inlineStr"/>
+      <c r="N560" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N560"/>
+  <dimension ref="A1:N563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20227,6 +20227,114 @@
       <c r="M560" t="inlineStr"/>
       <c r="N560" t="inlineStr"/>
     </row>
+    <row r="561">
+      <c r="A561" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B561" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C561" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D561" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E561" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F561" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G561" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H561" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I561" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J561" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K561" t="inlineStr"/>
+      <c r="L561" t="inlineStr"/>
+      <c r="M561" t="inlineStr"/>
+      <c r="N561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B562" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C562" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D562" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E562" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F562" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G562" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H562" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I562" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J562" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K562" t="inlineStr"/>
+      <c r="L562" t="inlineStr"/>
+      <c r="M562" t="inlineStr"/>
+      <c r="N562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B563" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C563" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D563" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E563" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G563" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H563" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I563" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J563" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr"/>
+      <c r="M563" t="inlineStr"/>
+      <c r="N563" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N563"/>
+  <dimension ref="A1:N565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20335,6 +20335,78 @@
       <c r="M563" t="inlineStr"/>
       <c r="N563" t="inlineStr"/>
     </row>
+    <row r="564">
+      <c r="A564" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B564" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C564" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D564" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E564" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G564" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H564" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I564" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J564" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr"/>
+      <c r="M564" t="inlineStr"/>
+      <c r="N564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B565" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C565" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D565" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E565" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G565" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H565" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I565" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J565" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr"/>
+      <c r="M565" t="inlineStr"/>
+      <c r="N565" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N565"/>
+  <dimension ref="A1:N569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20407,6 +20407,150 @@
       <c r="M565" t="inlineStr"/>
       <c r="N565" t="inlineStr"/>
     </row>
+    <row r="566">
+      <c r="A566" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B566" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C566" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D566" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E566" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G566" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H566" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I566" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J566" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr"/>
+      <c r="M566" t="inlineStr"/>
+      <c r="N566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B567" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C567" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D567" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E567" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G567" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H567" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I567" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J567" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr"/>
+      <c r="M567" t="inlineStr"/>
+      <c r="N567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B568" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C568" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D568" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E568" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F568" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G568" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H568" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I568" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J568" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr"/>
+      <c r="M568" t="inlineStr"/>
+      <c r="N568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B569" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C569" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D569" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E569" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F569" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G569" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H569" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I569" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J569" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr"/>
+      <c r="M569" t="inlineStr"/>
+      <c r="N569" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N569"/>
+  <dimension ref="A1:N575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20551,6 +20551,222 @@
       <c r="M569" t="inlineStr"/>
       <c r="N569" t="inlineStr"/>
     </row>
+    <row r="570">
+      <c r="A570" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B570" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C570" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D570" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E570" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F570" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G570" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H570" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I570" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J570" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr"/>
+      <c r="M570" t="inlineStr"/>
+      <c r="N570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="2" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B571" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C571" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D571" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E571" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G571" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H571" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I571" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J571" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr"/>
+      <c r="M571" t="inlineStr"/>
+      <c r="N571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B572" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C572" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D572" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E572" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G572" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H572" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I572" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J572" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr"/>
+      <c r="M572" t="inlineStr"/>
+      <c r="N572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B573" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C573" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D573" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E573" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F573" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G573" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H573" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I573" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J573" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K573" t="inlineStr"/>
+      <c r="L573" t="inlineStr"/>
+      <c r="M573" t="inlineStr"/>
+      <c r="N573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="2" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B574" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C574" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D574" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E574" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G574" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H574" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I574" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J574" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K574" t="inlineStr"/>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr"/>
+      <c r="N574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B575" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C575" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D575" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E575" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G575" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H575" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I575" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J575" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K575" t="inlineStr"/>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr"/>
+      <c r="N575" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N575"/>
+  <dimension ref="A1:N576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20767,6 +20767,42 @@
       <c r="M575" t="inlineStr"/>
       <c r="N575" t="inlineStr"/>
     </row>
+    <row r="576">
+      <c r="A576" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B576" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C576" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D576" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E576" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G576" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H576" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I576" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J576" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K576" t="inlineStr"/>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr"/>
+      <c r="N576" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N576"/>
+  <dimension ref="A1:N577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20803,6 +20803,42 @@
       <c r="M576" t="inlineStr"/>
       <c r="N576" t="inlineStr"/>
     </row>
+    <row r="577">
+      <c r="A577" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B577" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C577" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D577" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E577" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G577" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H577" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I577" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J577" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K577" t="inlineStr"/>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr"/>
+      <c r="N577" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N577"/>
+  <dimension ref="A1:N583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20839,6 +20839,222 @@
       <c r="M577" t="inlineStr"/>
       <c r="N577" t="inlineStr"/>
     </row>
+    <row r="578">
+      <c r="A578" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B578" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C578" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D578" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E578" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G578" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H578" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I578" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J578" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K578" t="inlineStr"/>
+      <c r="L578" t="inlineStr"/>
+      <c r="M578" t="inlineStr"/>
+      <c r="N578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B579" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C579" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D579" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E579" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G579" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H579" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I579" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J579" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K579" t="inlineStr"/>
+      <c r="L579" t="inlineStr"/>
+      <c r="M579" t="inlineStr"/>
+      <c r="N579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="2" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B580" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C580" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D580" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E580" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G580" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H580" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I580" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J580" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K580" t="inlineStr"/>
+      <c r="L580" t="inlineStr"/>
+      <c r="M580" t="inlineStr"/>
+      <c r="N580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="2" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B581" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C581" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D581" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E581" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G581" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H581" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I581" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J581" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K581" t="inlineStr"/>
+      <c r="L581" t="inlineStr"/>
+      <c r="M581" t="inlineStr"/>
+      <c r="N581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B582" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C582" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D582" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E582" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G582" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H582" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I582" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J582" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K582" t="inlineStr"/>
+      <c r="L582" t="inlineStr"/>
+      <c r="M582" t="inlineStr"/>
+      <c r="N582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B583" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C583" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D583" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E583" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F583" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G583" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H583" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I583" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J583" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K583" t="inlineStr"/>
+      <c r="L583" t="inlineStr"/>
+      <c r="M583" t="inlineStr"/>
+      <c r="N583" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N583"/>
+  <dimension ref="A1:N584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21055,6 +21055,42 @@
       <c r="M583" t="inlineStr"/>
       <c r="N583" t="inlineStr"/>
     </row>
+    <row r="584">
+      <c r="A584" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B584" t="n">
+        <v>0.70654272</v>
+      </c>
+      <c r="C584" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="D584" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="E584" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G584" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="H584" t="n">
+        <v>4106.72185423</v>
+      </c>
+      <c r="I584" t="n">
+        <v>0.02165823</v>
+      </c>
+      <c r="J584" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="K584" t="inlineStr"/>
+      <c r="L584" t="inlineStr"/>
+      <c r="M584" t="inlineStr"/>
+      <c r="N584" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P588"/>
+  <dimension ref="A1:P590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22427,6 +22427,90 @@
       <c r="O588" t="inlineStr"/>
       <c r="P588" t="inlineStr"/>
     </row>
+    <row r="589">
+      <c r="A589" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B589" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C589" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D589" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E589" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F589" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G589" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H589" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I589" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J589" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K589" t="n">
+        <v>185</v>
+      </c>
+      <c r="L589" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M589" t="inlineStr"/>
+      <c r="N589" t="inlineStr"/>
+      <c r="O589" t="inlineStr"/>
+      <c r="P589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B590" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C590" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D590" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E590" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F590" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G590" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H590" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I590" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J590" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K590" t="n">
+        <v>185</v>
+      </c>
+      <c r="L590" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M590" t="inlineStr"/>
+      <c r="N590" t="inlineStr"/>
+      <c r="O590" t="inlineStr"/>
+      <c r="P590" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P590"/>
+  <dimension ref="A1:P593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22511,6 +22511,132 @@
       <c r="O590" t="inlineStr"/>
       <c r="P590" t="inlineStr"/>
     </row>
+    <row r="591">
+      <c r="A591" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B591" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C591" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D591" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E591" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F591" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G591" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H591" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I591" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J591" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K591" t="n">
+        <v>185</v>
+      </c>
+      <c r="L591" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M591" t="inlineStr"/>
+      <c r="N591" t="inlineStr"/>
+      <c r="O591" t="inlineStr"/>
+      <c r="P591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B592" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C592" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D592" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E592" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F592" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G592" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H592" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I592" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J592" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K592" t="n">
+        <v>185</v>
+      </c>
+      <c r="L592" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M592" t="inlineStr"/>
+      <c r="N592" t="inlineStr"/>
+      <c r="O592" t="inlineStr"/>
+      <c r="P592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B593" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C593" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D593" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E593" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F593" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G593" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H593" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I593" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J593" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K593" t="n">
+        <v>185</v>
+      </c>
+      <c r="L593" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M593" t="inlineStr"/>
+      <c r="N593" t="inlineStr"/>
+      <c r="O593" t="inlineStr"/>
+      <c r="P593" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P593"/>
+  <dimension ref="A1:P595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22637,6 +22637,90 @@
       <c r="O593" t="inlineStr"/>
       <c r="P593" t="inlineStr"/>
     </row>
+    <row r="594">
+      <c r="A594" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B594" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C594" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D594" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E594" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F594" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G594" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H594" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I594" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J594" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K594" t="n">
+        <v>185</v>
+      </c>
+      <c r="L594" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M594" t="inlineStr"/>
+      <c r="N594" t="inlineStr"/>
+      <c r="O594" t="inlineStr"/>
+      <c r="P594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B595" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C595" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D595" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E595" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F595" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G595" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H595" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I595" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J595" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K595" t="n">
+        <v>185</v>
+      </c>
+      <c r="L595" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M595" t="inlineStr"/>
+      <c r="N595" t="inlineStr"/>
+      <c r="O595" t="inlineStr"/>
+      <c r="P595" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P595"/>
+  <dimension ref="A1:P599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22721,6 +22721,174 @@
       <c r="O595" t="inlineStr"/>
       <c r="P595" t="inlineStr"/>
     </row>
+    <row r="596">
+      <c r="A596" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B596" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C596" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D596" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E596" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F596" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G596" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H596" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I596" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J596" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K596" t="n">
+        <v>185</v>
+      </c>
+      <c r="L596" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M596" t="inlineStr"/>
+      <c r="N596" t="inlineStr"/>
+      <c r="O596" t="inlineStr"/>
+      <c r="P596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B597" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C597" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D597" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E597" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F597" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G597" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H597" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I597" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J597" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K597" t="n">
+        <v>185</v>
+      </c>
+      <c r="L597" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M597" t="inlineStr"/>
+      <c r="N597" t="inlineStr"/>
+      <c r="O597" t="inlineStr"/>
+      <c r="P597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B598" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C598" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D598" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E598" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F598" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G598" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H598" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I598" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J598" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K598" t="n">
+        <v>185</v>
+      </c>
+      <c r="L598" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M598" t="inlineStr"/>
+      <c r="N598" t="inlineStr"/>
+      <c r="O598" t="inlineStr"/>
+      <c r="P598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B599" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C599" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D599" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E599" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F599" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G599" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H599" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I599" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J599" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K599" t="n">
+        <v>185</v>
+      </c>
+      <c r="L599" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M599" t="inlineStr"/>
+      <c r="N599" t="inlineStr"/>
+      <c r="O599" t="inlineStr"/>
+      <c r="P599" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P599"/>
+  <dimension ref="A1:P600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22889,6 +22889,48 @@
       <c r="O599" t="inlineStr"/>
       <c r="P599" t="inlineStr"/>
     </row>
+    <row r="600">
+      <c r="A600" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B600" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C600" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D600" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E600" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F600" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G600" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H600" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I600" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J600" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K600" t="n">
+        <v>185</v>
+      </c>
+      <c r="L600" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M600" t="inlineStr"/>
+      <c r="N600" t="inlineStr"/>
+      <c r="O600" t="inlineStr"/>
+      <c r="P600" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P600"/>
+  <dimension ref="A1:P602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22931,6 +22931,90 @@
       <c r="O600" t="inlineStr"/>
       <c r="P600" t="inlineStr"/>
     </row>
+    <row r="601">
+      <c r="A601" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B601" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C601" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D601" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E601" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F601" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G601" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H601" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I601" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J601" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K601" t="n">
+        <v>185</v>
+      </c>
+      <c r="L601" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M601" t="inlineStr"/>
+      <c r="N601" t="inlineStr"/>
+      <c r="O601" t="inlineStr"/>
+      <c r="P601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B602" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C602" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D602" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E602" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F602" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G602" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H602" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I602" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J602" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K602" t="n">
+        <v>185</v>
+      </c>
+      <c r="L602" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M602" t="inlineStr"/>
+      <c r="N602" t="inlineStr"/>
+      <c r="O602" t="inlineStr"/>
+      <c r="P602" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P602"/>
+  <dimension ref="A1:P605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23015,6 +23015,132 @@
       <c r="O602" t="inlineStr"/>
       <c r="P602" t="inlineStr"/>
     </row>
+    <row r="603">
+      <c r="A603" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B603" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C603" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D603" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E603" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F603" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G603" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H603" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I603" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J603" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K603" t="n">
+        <v>185</v>
+      </c>
+      <c r="L603" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M603" t="inlineStr"/>
+      <c r="N603" t="inlineStr"/>
+      <c r="O603" t="inlineStr"/>
+      <c r="P603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B604" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C604" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D604" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E604" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F604" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G604" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H604" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I604" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J604" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K604" t="n">
+        <v>185</v>
+      </c>
+      <c r="L604" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M604" t="inlineStr"/>
+      <c r="N604" t="inlineStr"/>
+      <c r="O604" t="inlineStr"/>
+      <c r="P604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B605" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C605" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D605" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E605" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F605" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G605" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H605" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I605" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J605" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K605" t="n">
+        <v>185</v>
+      </c>
+      <c r="L605" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M605" t="inlineStr"/>
+      <c r="N605" t="inlineStr"/>
+      <c r="O605" t="inlineStr"/>
+      <c r="P605" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P605"/>
+  <dimension ref="A1:P606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23141,6 +23141,48 @@
       <c r="O605" t="inlineStr"/>
       <c r="P605" t="inlineStr"/>
     </row>
+    <row r="606">
+      <c r="A606" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B606" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C606" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D606" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E606" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F606" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G606" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H606" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I606" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J606" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K606" t="n">
+        <v>185</v>
+      </c>
+      <c r="L606" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M606" t="inlineStr"/>
+      <c r="N606" t="inlineStr"/>
+      <c r="O606" t="inlineStr"/>
+      <c r="P606" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P606"/>
+  <dimension ref="A1:P607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23183,6 +23183,48 @@
       <c r="O606" t="inlineStr"/>
       <c r="P606" t="inlineStr"/>
     </row>
+    <row r="607">
+      <c r="A607" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B607" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C607" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D607" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E607" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F607" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G607" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H607" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I607" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J607" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K607" t="n">
+        <v>185</v>
+      </c>
+      <c r="L607" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M607" t="inlineStr"/>
+      <c r="N607" t="inlineStr"/>
+      <c r="O607" t="inlineStr"/>
+      <c r="P607" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P607"/>
+  <dimension ref="A1:P610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23225,6 +23225,132 @@
       <c r="O607" t="inlineStr"/>
       <c r="P607" t="inlineStr"/>
     </row>
+    <row r="608">
+      <c r="A608" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B608" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C608" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D608" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E608" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F608" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G608" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H608" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I608" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J608" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K608" t="n">
+        <v>185</v>
+      </c>
+      <c r="L608" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M608" t="inlineStr"/>
+      <c r="N608" t="inlineStr"/>
+      <c r="O608" t="inlineStr"/>
+      <c r="P608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B609" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C609" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D609" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E609" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F609" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G609" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H609" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I609" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J609" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K609" t="n">
+        <v>185</v>
+      </c>
+      <c r="L609" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M609" t="inlineStr"/>
+      <c r="N609" t="inlineStr"/>
+      <c r="O609" t="inlineStr"/>
+      <c r="P609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B610" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C610" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D610" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E610" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F610" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G610" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H610" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I610" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J610" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K610" t="n">
+        <v>185</v>
+      </c>
+      <c r="L610" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M610" t="inlineStr"/>
+      <c r="N610" t="inlineStr"/>
+      <c r="O610" t="inlineStr"/>
+      <c r="P610" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P610"/>
+  <dimension ref="A1:P611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23351,6 +23351,48 @@
       <c r="O610" t="inlineStr"/>
       <c r="P610" t="inlineStr"/>
     </row>
+    <row r="611">
+      <c r="A611" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B611" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C611" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D611" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E611" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F611" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G611" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H611" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I611" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J611" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K611" t="n">
+        <v>185</v>
+      </c>
+      <c r="L611" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M611" t="inlineStr"/>
+      <c r="N611" t="inlineStr"/>
+      <c r="O611" t="inlineStr"/>
+      <c r="P611" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P611"/>
+  <dimension ref="A1:P612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23393,6 +23393,48 @@
       <c r="O611" t="inlineStr"/>
       <c r="P611" t="inlineStr"/>
     </row>
+    <row r="612">
+      <c r="A612" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B612" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C612" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D612" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E612" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F612" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G612" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H612" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I612" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J612" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K612" t="n">
+        <v>185</v>
+      </c>
+      <c r="L612" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M612" t="inlineStr"/>
+      <c r="N612" t="inlineStr"/>
+      <c r="O612" t="inlineStr"/>
+      <c r="P612" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P612"/>
+  <dimension ref="A1:P613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23435,6 +23435,48 @@
       <c r="O612" t="inlineStr"/>
       <c r="P612" t="inlineStr"/>
     </row>
+    <row r="613">
+      <c r="A613" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B613" t="n">
+        <v>0.72745565</v>
+      </c>
+      <c r="C613" t="n">
+        <v>1.002e-05</v>
+      </c>
+      <c r="D613" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E613" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F613" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="G613" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H613" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="I613" t="n">
+        <v>4476.47025923</v>
+      </c>
+      <c r="J613" t="n">
+        <v>0.02843823</v>
+      </c>
+      <c r="K613" t="n">
+        <v>185</v>
+      </c>
+      <c r="L613" t="n">
+        <v>0.6333977</v>
+      </c>
+      <c r="M613" t="inlineStr"/>
+      <c r="N613" t="inlineStr"/>
+      <c r="O613" t="inlineStr"/>
+      <c r="P613" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q619"/>
+  <dimension ref="A1:Q620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24358,6 +24358,51 @@
       <c r="P619" t="inlineStr"/>
       <c r="Q619" t="inlineStr"/>
     </row>
+    <row r="620">
+      <c r="A620" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B620" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C620" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D620" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E620" t="inlineStr"/>
+      <c r="F620" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G620" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H620" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I620" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J620" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K620" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L620" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M620" t="n">
+        <v>719</v>
+      </c>
+      <c r="N620" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O620" t="inlineStr"/>
+      <c r="P620" t="inlineStr"/>
+      <c r="Q620" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q620"/>
+  <dimension ref="A1:Q622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24403,6 +24403,96 @@
       <c r="P620" t="inlineStr"/>
       <c r="Q620" t="inlineStr"/>
     </row>
+    <row r="621">
+      <c r="A621" s="2" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B621" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C621" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D621" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E621" t="inlineStr"/>
+      <c r="F621" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G621" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H621" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I621" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J621" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K621" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L621" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M621" t="n">
+        <v>719</v>
+      </c>
+      <c r="N621" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O621" t="inlineStr"/>
+      <c r="P621" t="inlineStr"/>
+      <c r="Q621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B622" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C622" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D622" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E622" t="inlineStr"/>
+      <c r="F622" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G622" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H622" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I622" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J622" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K622" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L622" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M622" t="n">
+        <v>719</v>
+      </c>
+      <c r="N622" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O622" t="inlineStr"/>
+      <c r="P622" t="inlineStr"/>
+      <c r="Q622" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q622"/>
+  <dimension ref="A1:Q625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24493,6 +24493,141 @@
       <c r="P622" t="inlineStr"/>
       <c r="Q622" t="inlineStr"/>
     </row>
+    <row r="623">
+      <c r="A623" s="2" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B623" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C623" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D623" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E623" t="inlineStr"/>
+      <c r="F623" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G623" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H623" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I623" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J623" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K623" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L623" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M623" t="n">
+        <v>719</v>
+      </c>
+      <c r="N623" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O623" t="inlineStr"/>
+      <c r="P623" t="inlineStr"/>
+      <c r="Q623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="2" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B624" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C624" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D624" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E624" t="inlineStr"/>
+      <c r="F624" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G624" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H624" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I624" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J624" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K624" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L624" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M624" t="n">
+        <v>719</v>
+      </c>
+      <c r="N624" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O624" t="inlineStr"/>
+      <c r="P624" t="inlineStr"/>
+      <c r="Q624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B625" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C625" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D625" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E625" t="inlineStr"/>
+      <c r="F625" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G625" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H625" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I625" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J625" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K625" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L625" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M625" t="n">
+        <v>719</v>
+      </c>
+      <c r="N625" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O625" t="inlineStr"/>
+      <c r="P625" t="inlineStr"/>
+      <c r="Q625" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q625"/>
+  <dimension ref="A1:Q626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24628,6 +24628,51 @@
       <c r="P625" t="inlineStr"/>
       <c r="Q625" t="inlineStr"/>
     </row>
+    <row r="626">
+      <c r="A626" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B626" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C626" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D626" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E626" t="inlineStr"/>
+      <c r="F626" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G626" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H626" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I626" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J626" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K626" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L626" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M626" t="n">
+        <v>719</v>
+      </c>
+      <c r="N626" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O626" t="inlineStr"/>
+      <c r="P626" t="inlineStr"/>
+      <c r="Q626" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q626"/>
+  <dimension ref="A1:Q628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24673,6 +24673,96 @@
       <c r="P626" t="inlineStr"/>
       <c r="Q626" t="inlineStr"/>
     </row>
+    <row r="627">
+      <c r="A627" s="2" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B627" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C627" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D627" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E627" t="inlineStr"/>
+      <c r="F627" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G627" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H627" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I627" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J627" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K627" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L627" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M627" t="n">
+        <v>719</v>
+      </c>
+      <c r="N627" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O627" t="inlineStr"/>
+      <c r="P627" t="inlineStr"/>
+      <c r="Q627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B628" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C628" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D628" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E628" t="inlineStr"/>
+      <c r="F628" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G628" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H628" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I628" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J628" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K628" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L628" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M628" t="n">
+        <v>719</v>
+      </c>
+      <c r="N628" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O628" t="inlineStr"/>
+      <c r="P628" t="inlineStr"/>
+      <c r="Q628" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q628"/>
+  <dimension ref="A1:Q630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24763,6 +24763,96 @@
       <c r="P628" t="inlineStr"/>
       <c r="Q628" t="inlineStr"/>
     </row>
+    <row r="629">
+      <c r="A629" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B629" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C629" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D629" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E629" t="inlineStr"/>
+      <c r="F629" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G629" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H629" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I629" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J629" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K629" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L629" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M629" t="n">
+        <v>719</v>
+      </c>
+      <c r="N629" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O629" t="inlineStr"/>
+      <c r="P629" t="inlineStr"/>
+      <c r="Q629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="2" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B630" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C630" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D630" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E630" t="inlineStr"/>
+      <c r="F630" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G630" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H630" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I630" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J630" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K630" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L630" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M630" t="n">
+        <v>719</v>
+      </c>
+      <c r="N630" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O630" t="inlineStr"/>
+      <c r="P630" t="inlineStr"/>
+      <c r="Q630" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q630"/>
+  <dimension ref="A1:Q633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24853,6 +24853,135 @@
       <c r="P630" t="inlineStr"/>
       <c r="Q630" t="inlineStr"/>
     </row>
+    <row r="631">
+      <c r="A631" s="2" t="n">
+        <v>46187</v>
+      </c>
+      <c r="B631" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C631" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D631" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E631" t="inlineStr"/>
+      <c r="F631" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G631" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H631" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I631" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J631" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K631" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L631" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M631" t="n">
+        <v>719</v>
+      </c>
+      <c r="N631" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O631" t="inlineStr"/>
+      <c r="P631" t="inlineStr"/>
+      <c r="Q631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B632" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C632" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D632" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E632" t="inlineStr"/>
+      <c r="F632" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G632" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H632" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I632" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J632" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K632" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L632" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M632" t="n">
+        <v>719</v>
+      </c>
+      <c r="N632" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O632" t="inlineStr"/>
+      <c r="P632" t="inlineStr"/>
+      <c r="Q632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B633" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C633" t="inlineStr"/>
+      <c r="D633" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E633" t="inlineStr"/>
+      <c r="F633" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G633" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H633" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I633" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J633" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K633" t="inlineStr"/>
+      <c r="L633" t="inlineStr"/>
+      <c r="M633" t="n">
+        <v>719</v>
+      </c>
+      <c r="N633" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O633" t="inlineStr"/>
+      <c r="P633" t="inlineStr"/>
+      <c r="Q633" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -24950,7 +24950,9 @@
       <c r="B633" t="n">
         <v>0.00045565</v>
       </c>
-      <c r="C633" t="inlineStr"/>
+      <c r="C633" t="n">
+        <v>0.25259018</v>
+      </c>
       <c r="D633" t="n">
         <v>7.45e-06</v>
       </c>
@@ -24970,8 +24972,12 @@
       <c r="J633" t="n">
         <v>0.0004431</v>
       </c>
-      <c r="K633" t="inlineStr"/>
-      <c r="L633" t="inlineStr"/>
+      <c r="K633" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L633" t="n">
+        <v>0.49034888</v>
+      </c>
       <c r="M633" t="n">
         <v>719</v>
       </c>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q633"/>
+  <dimension ref="A1:Q636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24988,6 +24988,141 @@
       <c r="P633" t="inlineStr"/>
       <c r="Q633" t="inlineStr"/>
     </row>
+    <row r="634">
+      <c r="A634" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B634" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C634" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D634" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E634" t="inlineStr"/>
+      <c r="F634" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G634" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H634" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I634" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J634" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K634" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L634" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M634" t="n">
+        <v>719</v>
+      </c>
+      <c r="N634" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O634" t="inlineStr"/>
+      <c r="P634" t="inlineStr"/>
+      <c r="Q634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B635" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C635" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D635" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E635" t="inlineStr"/>
+      <c r="F635" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G635" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H635" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I635" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J635" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K635" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L635" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M635" t="n">
+        <v>719</v>
+      </c>
+      <c r="N635" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O635" t="inlineStr"/>
+      <c r="P635" t="inlineStr"/>
+      <c r="Q635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B636" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C636" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D636" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E636" t="inlineStr"/>
+      <c r="F636" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G636" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H636" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I636" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J636" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K636" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L636" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M636" t="n">
+        <v>719</v>
+      </c>
+      <c r="N636" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O636" t="inlineStr"/>
+      <c r="P636" t="inlineStr"/>
+      <c r="Q636" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q636"/>
+  <dimension ref="A1:Q638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25123,6 +25123,96 @@
       <c r="P636" t="inlineStr"/>
       <c r="Q636" t="inlineStr"/>
     </row>
+    <row r="637">
+      <c r="A637" s="2" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B637" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C637" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D637" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E637" t="inlineStr"/>
+      <c r="F637" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G637" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H637" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I637" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J637" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K637" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L637" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M637" t="n">
+        <v>719</v>
+      </c>
+      <c r="N637" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O637" t="inlineStr"/>
+      <c r="P637" t="inlineStr"/>
+      <c r="Q637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="2" t="n">
+        <v>46194</v>
+      </c>
+      <c r="B638" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C638" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D638" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E638" t="inlineStr"/>
+      <c r="F638" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G638" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H638" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I638" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J638" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K638" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L638" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M638" t="n">
+        <v>719</v>
+      </c>
+      <c r="N638" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O638" t="inlineStr"/>
+      <c r="P638" t="inlineStr"/>
+      <c r="Q638" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q638"/>
+  <dimension ref="A1:Q640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25213,6 +25213,96 @@
       <c r="P638" t="inlineStr"/>
       <c r="Q638" t="inlineStr"/>
     </row>
+    <row r="639">
+      <c r="A639" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B639" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C639" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D639" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E639" t="inlineStr"/>
+      <c r="F639" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G639" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H639" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I639" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J639" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K639" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L639" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M639" t="n">
+        <v>719</v>
+      </c>
+      <c r="N639" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O639" t="inlineStr"/>
+      <c r="P639" t="inlineStr"/>
+      <c r="Q639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B640" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C640" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D640" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E640" t="inlineStr"/>
+      <c r="F640" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G640" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H640" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I640" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J640" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K640" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L640" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M640" t="n">
+        <v>719</v>
+      </c>
+      <c r="N640" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O640" t="inlineStr"/>
+      <c r="P640" t="inlineStr"/>
+      <c r="Q640" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q640"/>
+  <dimension ref="A1:Q641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25303,6 +25303,51 @@
       <c r="P640" t="inlineStr"/>
       <c r="Q640" t="inlineStr"/>
     </row>
+    <row r="641">
+      <c r="A641" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B641" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C641" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D641" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E641" t="inlineStr"/>
+      <c r="F641" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G641" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H641" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I641" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J641" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K641" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L641" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M641" t="n">
+        <v>719</v>
+      </c>
+      <c r="N641" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O641" t="inlineStr"/>
+      <c r="P641" t="inlineStr"/>
+      <c r="Q641" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q641"/>
+  <dimension ref="A1:Q643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25348,6 +25348,96 @@
       <c r="P641" t="inlineStr"/>
       <c r="Q641" t="inlineStr"/>
     </row>
+    <row r="642">
+      <c r="A642" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B642" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C642" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D642" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E642" t="inlineStr"/>
+      <c r="F642" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G642" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H642" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I642" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J642" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K642" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L642" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M642" t="n">
+        <v>719</v>
+      </c>
+      <c r="N642" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O642" t="inlineStr"/>
+      <c r="P642" t="inlineStr"/>
+      <c r="Q642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B643" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C643" t="n">
+        <v>0.25259018</v>
+      </c>
+      <c r="D643" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E643" t="inlineStr"/>
+      <c r="F643" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="G643" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="H643" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="I643" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J643" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="K643" t="n">
+        <v>4051.37025923</v>
+      </c>
+      <c r="L643" t="n">
+        <v>0.49034888</v>
+      </c>
+      <c r="M643" t="n">
+        <v>719</v>
+      </c>
+      <c r="N643" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="O643" t="inlineStr"/>
+      <c r="P643" t="inlineStr"/>
+      <c r="Q643" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q646"/>
+  <dimension ref="A1:Q647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25573,6 +25573,49 @@
       <c r="P646" t="inlineStr"/>
       <c r="Q646" t="inlineStr"/>
     </row>
+    <row r="647">
+      <c r="A647" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B647" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C647" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D647" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E647" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F647" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G647" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H647" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I647" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J647" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K647" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L647" t="inlineStr"/>
+      <c r="M647" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N647" t="inlineStr"/>
+      <c r="O647" t="inlineStr"/>
+      <c r="P647" t="inlineStr"/>
+      <c r="Q647" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q647"/>
+  <dimension ref="A1:Q650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25616,6 +25616,135 @@
       <c r="P647" t="inlineStr"/>
       <c r="Q647" t="inlineStr"/>
     </row>
+    <row r="648">
+      <c r="A648" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B648" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C648" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D648" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E648" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F648" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G648" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H648" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I648" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J648" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K648" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L648" t="inlineStr"/>
+      <c r="M648" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N648" t="inlineStr"/>
+      <c r="O648" t="inlineStr"/>
+      <c r="P648" t="inlineStr"/>
+      <c r="Q648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B649" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C649" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D649" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E649" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F649" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G649" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H649" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I649" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J649" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K649" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L649" t="inlineStr"/>
+      <c r="M649" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N649" t="inlineStr"/>
+      <c r="O649" t="inlineStr"/>
+      <c r="P649" t="inlineStr"/>
+      <c r="Q649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B650" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C650" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D650" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E650" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F650" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G650" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H650" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I650" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J650" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K650" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L650" t="inlineStr"/>
+      <c r="M650" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N650" t="inlineStr"/>
+      <c r="O650" t="inlineStr"/>
+      <c r="P650" t="inlineStr"/>
+      <c r="Q650" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q650"/>
+  <dimension ref="A1:Q654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25745,6 +25745,178 @@
       <c r="P650" t="inlineStr"/>
       <c r="Q650" t="inlineStr"/>
     </row>
+    <row r="651">
+      <c r="A651" s="2" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B651" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C651" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D651" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E651" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F651" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G651" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H651" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I651" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J651" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K651" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N651" t="inlineStr"/>
+      <c r="O651" t="inlineStr"/>
+      <c r="P651" t="inlineStr"/>
+      <c r="Q651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="2" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B652" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C652" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D652" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E652" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F652" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G652" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H652" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I652" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J652" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K652" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L652" t="inlineStr"/>
+      <c r="M652" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N652" t="inlineStr"/>
+      <c r="O652" t="inlineStr"/>
+      <c r="P652" t="inlineStr"/>
+      <c r="Q652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B653" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C653" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D653" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E653" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F653" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G653" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H653" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I653" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J653" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K653" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N653" t="inlineStr"/>
+      <c r="O653" t="inlineStr"/>
+      <c r="P653" t="inlineStr"/>
+      <c r="Q653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B654" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C654" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D654" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E654" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G654" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H654" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I654" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J654" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K654" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L654" t="inlineStr"/>
+      <c r="M654" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N654" t="inlineStr"/>
+      <c r="O654" t="inlineStr"/>
+      <c r="P654" t="inlineStr"/>
+      <c r="Q654" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q654"/>
+  <dimension ref="A1:Q656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25917,6 +25917,92 @@
       <c r="P654" t="inlineStr"/>
       <c r="Q654" t="inlineStr"/>
     </row>
+    <row r="655">
+      <c r="A655" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B655" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C655" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D655" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E655" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F655" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G655" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H655" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I655" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J655" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K655" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L655" t="inlineStr"/>
+      <c r="M655" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N655" t="inlineStr"/>
+      <c r="O655" t="inlineStr"/>
+      <c r="P655" t="inlineStr"/>
+      <c r="Q655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B656" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C656" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D656" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E656" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F656" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G656" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H656" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I656" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J656" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K656" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L656" t="inlineStr"/>
+      <c r="M656" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N656" t="inlineStr"/>
+      <c r="O656" t="inlineStr"/>
+      <c r="P656" t="inlineStr"/>
+      <c r="Q656" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q656"/>
+  <dimension ref="A1:Q657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26003,6 +26003,49 @@
       <c r="P656" t="inlineStr"/>
       <c r="Q656" t="inlineStr"/>
     </row>
+    <row r="657">
+      <c r="A657" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B657" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C657" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D657" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E657" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F657" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G657" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H657" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I657" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J657" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K657" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L657" t="inlineStr"/>
+      <c r="M657" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N657" t="inlineStr"/>
+      <c r="O657" t="inlineStr"/>
+      <c r="P657" t="inlineStr"/>
+      <c r="Q657" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q657"/>
+  <dimension ref="A1:Q658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26046,6 +26046,49 @@
       <c r="P657" t="inlineStr"/>
       <c r="Q657" t="inlineStr"/>
     </row>
+    <row r="658">
+      <c r="A658" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B658" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C658" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D658" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E658" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F658" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G658" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H658" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I658" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J658" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K658" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N658" t="inlineStr"/>
+      <c r="O658" t="inlineStr"/>
+      <c r="P658" t="inlineStr"/>
+      <c r="Q658" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q658"/>
+  <dimension ref="A1:Q660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26089,6 +26089,92 @@
       <c r="P658" t="inlineStr"/>
       <c r="Q658" t="inlineStr"/>
     </row>
+    <row r="659">
+      <c r="A659" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B659" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C659" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D659" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E659" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F659" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G659" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H659" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I659" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J659" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K659" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N659" t="inlineStr"/>
+      <c r="O659" t="inlineStr"/>
+      <c r="P659" t="inlineStr"/>
+      <c r="Q659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B660" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C660" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D660" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E660" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F660" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G660" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H660" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I660" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J660" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K660" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N660" t="inlineStr"/>
+      <c r="O660" t="inlineStr"/>
+      <c r="P660" t="inlineStr"/>
+      <c r="Q660" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q660"/>
+  <dimension ref="A1:Q661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26175,6 +26175,49 @@
       <c r="P660" t="inlineStr"/>
       <c r="Q660" t="inlineStr"/>
     </row>
+    <row r="661">
+      <c r="A661" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B661" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C661" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D661" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E661" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F661" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G661" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H661" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I661" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J661" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K661" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N661" t="inlineStr"/>
+      <c r="O661" t="inlineStr"/>
+      <c r="P661" t="inlineStr"/>
+      <c r="Q661" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q661"/>
+  <dimension ref="A1:Q663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26218,6 +26218,92 @@
       <c r="P661" t="inlineStr"/>
       <c r="Q661" t="inlineStr"/>
     </row>
+    <row r="662">
+      <c r="A662" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B662" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C662" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D662" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E662" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G662" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H662" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I662" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J662" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K662" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N662" t="inlineStr"/>
+      <c r="O662" t="inlineStr"/>
+      <c r="P662" t="inlineStr"/>
+      <c r="Q662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B663" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C663" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D663" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E663" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F663" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G663" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H663" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I663" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J663" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K663" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N663" t="inlineStr"/>
+      <c r="O663" t="inlineStr"/>
+      <c r="P663" t="inlineStr"/>
+      <c r="Q663" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q663"/>
+  <dimension ref="A1:Q664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26304,6 +26304,49 @@
       <c r="P663" t="inlineStr"/>
       <c r="Q663" t="inlineStr"/>
     </row>
+    <row r="664">
+      <c r="A664" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B664" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C664" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D664" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E664" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F664" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G664" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H664" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I664" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J664" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K664" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L664" t="inlineStr"/>
+      <c r="M664" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N664" t="inlineStr"/>
+      <c r="O664" t="inlineStr"/>
+      <c r="P664" t="inlineStr"/>
+      <c r="Q664" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q664"/>
+  <dimension ref="A1:Q666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26347,6 +26347,92 @@
       <c r="P664" t="inlineStr"/>
       <c r="Q664" t="inlineStr"/>
     </row>
+    <row r="665">
+      <c r="A665" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B665" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C665" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D665" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E665" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F665" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G665" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H665" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I665" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J665" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K665" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N665" t="inlineStr"/>
+      <c r="O665" t="inlineStr"/>
+      <c r="P665" t="inlineStr"/>
+      <c r="Q665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B666" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C666" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D666" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E666" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F666" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G666" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H666" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I666" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J666" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K666" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L666" t="inlineStr"/>
+      <c r="M666" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N666" t="inlineStr"/>
+      <c r="O666" t="inlineStr"/>
+      <c r="P666" t="inlineStr"/>
+      <c r="Q666" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q666"/>
+  <dimension ref="A1:Q667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26433,6 +26433,49 @@
       <c r="P666" t="inlineStr"/>
       <c r="Q666" t="inlineStr"/>
     </row>
+    <row r="667">
+      <c r="A667" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B667" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C667" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D667" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E667" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F667" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G667" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H667" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I667" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J667" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K667" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L667" t="inlineStr"/>
+      <c r="M667" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N667" t="inlineStr"/>
+      <c r="O667" t="inlineStr"/>
+      <c r="P667" t="inlineStr"/>
+      <c r="Q667" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q667"/>
+  <dimension ref="A1:Q671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26476,6 +26476,178 @@
       <c r="P667" t="inlineStr"/>
       <c r="Q667" t="inlineStr"/>
     </row>
+    <row r="668">
+      <c r="A668" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B668" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C668" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D668" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E668" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F668" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G668" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H668" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I668" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J668" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K668" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N668" t="inlineStr"/>
+      <c r="O668" t="inlineStr"/>
+      <c r="P668" t="inlineStr"/>
+      <c r="Q668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B669" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C669" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D669" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E669" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G669" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H669" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I669" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J669" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K669" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N669" t="inlineStr"/>
+      <c r="O669" t="inlineStr"/>
+      <c r="P669" t="inlineStr"/>
+      <c r="Q669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B670" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C670" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D670" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E670" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G670" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H670" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I670" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J670" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K670" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L670" t="inlineStr"/>
+      <c r="M670" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N670" t="inlineStr"/>
+      <c r="O670" t="inlineStr"/>
+      <c r="P670" t="inlineStr"/>
+      <c r="Q670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B671" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C671" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D671" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E671" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F671" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G671" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H671" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I671" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J671" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K671" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L671" t="inlineStr"/>
+      <c r="M671" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="N671" t="inlineStr"/>
+      <c r="O671" t="inlineStr"/>
+      <c r="P671" t="inlineStr"/>
+      <c r="Q671" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q671"/>
+  <dimension ref="A1:Q675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,12 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>XLMUSDT</t>
+          <t>ZECUSDT</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ZECUSDT</t>
+          <t>XLMUSDT</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -17176,10 +17176,10 @@
       <c r="K434" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L434" t="inlineStr"/>
-      <c r="M434" t="n">
+      <c r="L434" t="n">
         <v>0.048</v>
       </c>
+      <c r="M434" t="inlineStr"/>
       <c r="N434" t="inlineStr"/>
       <c r="O434" t="n">
         <v>465.80531254</v>
@@ -17215,10 +17215,10 @@
       <c r="K435" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L435" t="inlineStr"/>
-      <c r="M435" t="n">
+      <c r="L435" t="n">
         <v>0.048</v>
       </c>
+      <c r="M435" t="inlineStr"/>
       <c r="N435" t="inlineStr"/>
       <c r="O435" t="n">
         <v>465.80531254</v>
@@ -17254,10 +17254,10 @@
       <c r="K436" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L436" t="inlineStr"/>
-      <c r="M436" t="n">
+      <c r="L436" t="n">
         <v>0.048</v>
       </c>
+      <c r="M436" t="inlineStr"/>
       <c r="N436" t="inlineStr"/>
       <c r="O436" t="n">
         <v>465.80531254</v>
@@ -17293,10 +17293,10 @@
       <c r="K437" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L437" t="inlineStr"/>
-      <c r="M437" t="n">
+      <c r="L437" t="n">
         <v>0.048</v>
       </c>
+      <c r="M437" t="inlineStr"/>
       <c r="N437" t="inlineStr"/>
       <c r="O437" t="n">
         <v>465.80531254</v>
@@ -17332,10 +17332,10 @@
       <c r="K438" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L438" t="inlineStr"/>
-      <c r="M438" t="n">
+      <c r="L438" t="n">
         <v>0.048</v>
       </c>
+      <c r="M438" t="inlineStr"/>
       <c r="N438" t="inlineStr"/>
       <c r="O438" t="n">
         <v>465.80531254</v>
@@ -17371,10 +17371,10 @@
       <c r="K439" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L439" t="inlineStr"/>
-      <c r="M439" t="n">
+      <c r="L439" t="n">
         <v>0.048</v>
       </c>
+      <c r="M439" t="inlineStr"/>
       <c r="N439" t="inlineStr"/>
       <c r="O439" t="n">
         <v>465.80531254</v>
@@ -17410,10 +17410,10 @@
       <c r="K440" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L440" t="inlineStr"/>
-      <c r="M440" t="n">
+      <c r="L440" t="n">
         <v>0.048</v>
       </c>
+      <c r="M440" t="inlineStr"/>
       <c r="N440" t="inlineStr"/>
       <c r="O440" t="n">
         <v>465.80531254</v>
@@ -17449,10 +17449,10 @@
       <c r="K441" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L441" t="inlineStr"/>
-      <c r="M441" t="n">
+      <c r="L441" t="n">
         <v>0.048</v>
       </c>
+      <c r="M441" t="inlineStr"/>
       <c r="N441" t="inlineStr"/>
       <c r="O441" t="n">
         <v>465.80531254</v>
@@ -17488,10 +17488,10 @@
       <c r="K442" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L442" t="inlineStr"/>
-      <c r="M442" t="n">
+      <c r="L442" t="n">
         <v>0.048</v>
       </c>
+      <c r="M442" t="inlineStr"/>
       <c r="N442" t="inlineStr"/>
       <c r="O442" t="n">
         <v>465.80531254</v>
@@ -17527,10 +17527,10 @@
       <c r="K443" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L443" t="inlineStr"/>
-      <c r="M443" t="n">
+      <c r="L443" t="n">
         <v>0.048</v>
       </c>
+      <c r="M443" t="inlineStr"/>
       <c r="N443" t="inlineStr"/>
       <c r="O443" t="n">
         <v>465.80531254</v>
@@ -17566,10 +17566,10 @@
       <c r="K444" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L444" t="inlineStr"/>
-      <c r="M444" t="n">
+      <c r="L444" t="n">
         <v>0.048</v>
       </c>
+      <c r="M444" t="inlineStr"/>
       <c r="N444" t="inlineStr"/>
       <c r="O444" t="n">
         <v>465.80531254</v>
@@ -17605,10 +17605,10 @@
       <c r="K445" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L445" t="inlineStr"/>
-      <c r="M445" t="n">
+      <c r="L445" t="n">
         <v>0.048</v>
       </c>
+      <c r="M445" t="inlineStr"/>
       <c r="N445" t="inlineStr"/>
       <c r="O445" t="n">
         <v>465.80531254</v>
@@ -17644,10 +17644,10 @@
       <c r="K446" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L446" t="inlineStr"/>
-      <c r="M446" t="n">
+      <c r="L446" t="n">
         <v>0.048</v>
       </c>
+      <c r="M446" t="inlineStr"/>
       <c r="N446" t="inlineStr"/>
       <c r="O446" t="n">
         <v>465.80531254</v>
@@ -17683,10 +17683,10 @@
       <c r="K447" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L447" t="inlineStr"/>
-      <c r="M447" t="n">
+      <c r="L447" t="n">
         <v>0.048</v>
       </c>
+      <c r="M447" t="inlineStr"/>
       <c r="N447" t="inlineStr"/>
       <c r="O447" t="n">
         <v>465.80531254</v>
@@ -17722,10 +17722,10 @@
       <c r="K448" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L448" t="inlineStr"/>
-      <c r="M448" t="n">
+      <c r="L448" t="n">
         <v>0.048</v>
       </c>
+      <c r="M448" t="inlineStr"/>
       <c r="N448" t="inlineStr"/>
       <c r="O448" t="n">
         <v>465.80531254</v>
@@ -17761,10 +17761,10 @@
       <c r="K449" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L449" t="inlineStr"/>
-      <c r="M449" t="n">
+      <c r="L449" t="n">
         <v>0.048</v>
       </c>
+      <c r="M449" t="inlineStr"/>
       <c r="N449" t="inlineStr"/>
       <c r="O449" t="n">
         <v>465.80531254</v>
@@ -17800,10 +17800,10 @@
       <c r="K450" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L450" t="inlineStr"/>
-      <c r="M450" t="n">
+      <c r="L450" t="n">
         <v>0.048</v>
       </c>
+      <c r="M450" t="inlineStr"/>
       <c r="N450" t="inlineStr"/>
       <c r="O450" t="n">
         <v>465.80531254</v>
@@ -17839,10 +17839,10 @@
       <c r="K451" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L451" t="inlineStr"/>
-      <c r="M451" t="n">
+      <c r="L451" t="n">
         <v>0.048</v>
       </c>
+      <c r="M451" t="inlineStr"/>
       <c r="N451" t="inlineStr"/>
       <c r="O451" t="n">
         <v>465.80531254</v>
@@ -17878,10 +17878,10 @@
       <c r="K452" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L452" t="inlineStr"/>
-      <c r="M452" t="n">
+      <c r="L452" t="n">
         <v>0.048</v>
       </c>
+      <c r="M452" t="inlineStr"/>
       <c r="N452" t="inlineStr"/>
       <c r="O452" t="n">
         <v>465.80531254</v>
@@ -17917,10 +17917,10 @@
       <c r="K453" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L453" t="inlineStr"/>
-      <c r="M453" t="n">
+      <c r="L453" t="n">
         <v>0.048</v>
       </c>
+      <c r="M453" t="inlineStr"/>
       <c r="N453" t="inlineStr"/>
       <c r="O453" t="n">
         <v>465.80531254</v>
@@ -17956,10 +17956,10 @@
       <c r="K454" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L454" t="inlineStr"/>
-      <c r="M454" t="n">
+      <c r="L454" t="n">
         <v>0.048</v>
       </c>
+      <c r="M454" t="inlineStr"/>
       <c r="N454" t="inlineStr"/>
       <c r="O454" t="n">
         <v>465.80531254</v>
@@ -17995,10 +17995,10 @@
       <c r="K455" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L455" t="inlineStr"/>
-      <c r="M455" t="n">
+      <c r="L455" t="n">
         <v>0.048</v>
       </c>
+      <c r="M455" t="inlineStr"/>
       <c r="N455" t="inlineStr"/>
       <c r="O455" t="n">
         <v>465.80531254</v>
@@ -18034,10 +18034,10 @@
       <c r="K456" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L456" t="inlineStr"/>
-      <c r="M456" t="n">
+      <c r="L456" t="n">
         <v>0.048</v>
       </c>
+      <c r="M456" t="inlineStr"/>
       <c r="N456" t="inlineStr"/>
       <c r="O456" t="n">
         <v>465.80531254</v>
@@ -18073,10 +18073,10 @@
       <c r="K457" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L457" t="inlineStr"/>
-      <c r="M457" t="n">
+      <c r="L457" t="n">
         <v>0.048</v>
       </c>
+      <c r="M457" t="inlineStr"/>
       <c r="N457" t="inlineStr"/>
       <c r="O457" t="n">
         <v>465.80531254</v>
@@ -18112,10 +18112,10 @@
       <c r="K458" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L458" t="inlineStr"/>
-      <c r="M458" t="n">
+      <c r="L458" t="n">
         <v>0.048</v>
       </c>
+      <c r="M458" t="inlineStr"/>
       <c r="N458" t="inlineStr"/>
       <c r="O458" t="n">
         <v>465.80531254</v>
@@ -18151,10 +18151,10 @@
       <c r="K459" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L459" t="inlineStr"/>
-      <c r="M459" t="n">
+      <c r="L459" t="n">
         <v>0.048</v>
       </c>
+      <c r="M459" t="inlineStr"/>
       <c r="N459" t="inlineStr"/>
       <c r="O459" t="n">
         <v>465.80531254</v>
@@ -18190,10 +18190,10 @@
       <c r="K460" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L460" t="inlineStr"/>
-      <c r="M460" t="n">
+      <c r="L460" t="n">
         <v>0.048</v>
       </c>
+      <c r="M460" t="inlineStr"/>
       <c r="N460" t="inlineStr"/>
       <c r="O460" t="n">
         <v>465.80531254</v>
@@ -18229,10 +18229,10 @@
       <c r="K461" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L461" t="inlineStr"/>
-      <c r="M461" t="n">
+      <c r="L461" t="n">
         <v>0.048</v>
       </c>
+      <c r="M461" t="inlineStr"/>
       <c r="N461" t="inlineStr"/>
       <c r="O461" t="n">
         <v>465.80531254</v>
@@ -18268,10 +18268,10 @@
       <c r="K462" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L462" t="inlineStr"/>
-      <c r="M462" t="n">
+      <c r="L462" t="n">
         <v>0.048</v>
       </c>
+      <c r="M462" t="inlineStr"/>
       <c r="N462" t="inlineStr"/>
       <c r="O462" t="n">
         <v>465.80531254</v>
@@ -18307,10 +18307,10 @@
       <c r="K463" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L463" t="inlineStr"/>
-      <c r="M463" t="n">
+      <c r="L463" t="n">
         <v>0.048</v>
       </c>
+      <c r="M463" t="inlineStr"/>
       <c r="N463" t="inlineStr"/>
       <c r="O463" t="n">
         <v>465.80531254</v>
@@ -18346,10 +18346,10 @@
       <c r="K464" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L464" t="inlineStr"/>
-      <c r="M464" t="n">
+      <c r="L464" t="n">
         <v>0.048</v>
       </c>
+      <c r="M464" t="inlineStr"/>
       <c r="N464" t="inlineStr"/>
       <c r="O464" t="n">
         <v>465.80531254</v>
@@ -18385,10 +18385,10 @@
       <c r="K465" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L465" t="inlineStr"/>
-      <c r="M465" t="n">
+      <c r="L465" t="n">
         <v>0.048</v>
       </c>
+      <c r="M465" t="inlineStr"/>
       <c r="N465" t="inlineStr"/>
       <c r="O465" t="n">
         <v>465.80531254</v>
@@ -18424,10 +18424,10 @@
       <c r="K466" t="n">
         <v>0.00151947</v>
       </c>
-      <c r="L466" t="inlineStr"/>
-      <c r="M466" t="n">
+      <c r="L466" t="n">
         <v>0.048</v>
       </c>
+      <c r="M466" t="inlineStr"/>
       <c r="N466" t="inlineStr"/>
       <c r="O466" t="n">
         <v>465.80531254</v>
@@ -24258,10 +24258,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L617" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M617" t="n">
         <v>719</v>
-      </c>
-      <c r="M617" t="n">
-        <v>0.104</v>
       </c>
       <c r="N617" t="inlineStr"/>
       <c r="O617" t="inlineStr"/>
@@ -24303,10 +24303,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L618" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M618" t="n">
         <v>719</v>
-      </c>
-      <c r="M618" t="n">
-        <v>0.104</v>
       </c>
       <c r="N618" t="inlineStr"/>
       <c r="O618" t="inlineStr"/>
@@ -24348,10 +24348,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L619" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M619" t="n">
         <v>719</v>
-      </c>
-      <c r="M619" t="n">
-        <v>0.104</v>
       </c>
       <c r="N619" t="inlineStr"/>
       <c r="O619" t="inlineStr"/>
@@ -24393,10 +24393,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L620" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M620" t="n">
         <v>719</v>
-      </c>
-      <c r="M620" t="n">
-        <v>0.104</v>
       </c>
       <c r="N620" t="inlineStr"/>
       <c r="O620" t="inlineStr"/>
@@ -24438,10 +24438,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L621" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M621" t="n">
         <v>719</v>
-      </c>
-      <c r="M621" t="n">
-        <v>0.104</v>
       </c>
       <c r="N621" t="inlineStr"/>
       <c r="O621" t="inlineStr"/>
@@ -24483,10 +24483,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L622" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M622" t="n">
         <v>719</v>
-      </c>
-      <c r="M622" t="n">
-        <v>0.104</v>
       </c>
       <c r="N622" t="inlineStr"/>
       <c r="O622" t="inlineStr"/>
@@ -24528,10 +24528,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L623" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M623" t="n">
         <v>719</v>
-      </c>
-      <c r="M623" t="n">
-        <v>0.104</v>
       </c>
       <c r="N623" t="inlineStr"/>
       <c r="O623" t="inlineStr"/>
@@ -24573,10 +24573,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L624" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M624" t="n">
         <v>719</v>
-      </c>
-      <c r="M624" t="n">
-        <v>0.104</v>
       </c>
       <c r="N624" t="inlineStr"/>
       <c r="O624" t="inlineStr"/>
@@ -24618,10 +24618,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L625" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M625" t="n">
         <v>719</v>
-      </c>
-      <c r="M625" t="n">
-        <v>0.104</v>
       </c>
       <c r="N625" t="inlineStr"/>
       <c r="O625" t="inlineStr"/>
@@ -24663,10 +24663,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L626" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M626" t="n">
         <v>719</v>
-      </c>
-      <c r="M626" t="n">
-        <v>0.104</v>
       </c>
       <c r="N626" t="inlineStr"/>
       <c r="O626" t="inlineStr"/>
@@ -24708,10 +24708,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L627" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M627" t="n">
         <v>719</v>
-      </c>
-      <c r="M627" t="n">
-        <v>0.104</v>
       </c>
       <c r="N627" t="inlineStr"/>
       <c r="O627" t="inlineStr"/>
@@ -24753,10 +24753,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L628" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M628" t="n">
         <v>719</v>
-      </c>
-      <c r="M628" t="n">
-        <v>0.104</v>
       </c>
       <c r="N628" t="inlineStr"/>
       <c r="O628" t="inlineStr"/>
@@ -24798,10 +24798,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L629" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M629" t="n">
         <v>719</v>
-      </c>
-      <c r="M629" t="n">
-        <v>0.104</v>
       </c>
       <c r="N629" t="inlineStr"/>
       <c r="O629" t="inlineStr"/>
@@ -24843,10 +24843,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L630" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M630" t="n">
         <v>719</v>
-      </c>
-      <c r="M630" t="n">
-        <v>0.104</v>
       </c>
       <c r="N630" t="inlineStr"/>
       <c r="O630" t="inlineStr"/>
@@ -24888,10 +24888,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L631" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M631" t="n">
         <v>719</v>
-      </c>
-      <c r="M631" t="n">
-        <v>0.104</v>
       </c>
       <c r="N631" t="inlineStr"/>
       <c r="O631" t="inlineStr"/>
@@ -24933,10 +24933,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L632" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M632" t="n">
         <v>719</v>
-      </c>
-      <c r="M632" t="n">
-        <v>0.104</v>
       </c>
       <c r="N632" t="inlineStr"/>
       <c r="O632" t="inlineStr"/>
@@ -24978,10 +24978,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L633" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M633" t="n">
         <v>719</v>
-      </c>
-      <c r="M633" t="n">
-        <v>0.104</v>
       </c>
       <c r="N633" t="inlineStr"/>
       <c r="O633" t="inlineStr"/>
@@ -25023,10 +25023,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L634" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M634" t="n">
         <v>719</v>
-      </c>
-      <c r="M634" t="n">
-        <v>0.104</v>
       </c>
       <c r="N634" t="inlineStr"/>
       <c r="O634" t="inlineStr"/>
@@ -25068,10 +25068,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L635" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M635" t="n">
         <v>719</v>
-      </c>
-      <c r="M635" t="n">
-        <v>0.104</v>
       </c>
       <c r="N635" t="inlineStr"/>
       <c r="O635" t="inlineStr"/>
@@ -25113,10 +25113,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L636" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M636" t="n">
         <v>719</v>
-      </c>
-      <c r="M636" t="n">
-        <v>0.104</v>
       </c>
       <c r="N636" t="inlineStr"/>
       <c r="O636" t="inlineStr"/>
@@ -25158,10 +25158,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L637" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M637" t="n">
         <v>719</v>
-      </c>
-      <c r="M637" t="n">
-        <v>0.104</v>
       </c>
       <c r="N637" t="inlineStr"/>
       <c r="O637" t="inlineStr"/>
@@ -25203,10 +25203,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L638" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M638" t="n">
         <v>719</v>
-      </c>
-      <c r="M638" t="n">
-        <v>0.104</v>
       </c>
       <c r="N638" t="inlineStr"/>
       <c r="O638" t="inlineStr"/>
@@ -25248,10 +25248,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L639" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M639" t="n">
         <v>719</v>
-      </c>
-      <c r="M639" t="n">
-        <v>0.104</v>
       </c>
       <c r="N639" t="inlineStr"/>
       <c r="O639" t="inlineStr"/>
@@ -25293,10 +25293,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L640" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M640" t="n">
         <v>719</v>
-      </c>
-      <c r="M640" t="n">
-        <v>0.104</v>
       </c>
       <c r="N640" t="inlineStr"/>
       <c r="O640" t="inlineStr"/>
@@ -25338,10 +25338,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L641" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M641" t="n">
         <v>719</v>
-      </c>
-      <c r="M641" t="n">
-        <v>0.104</v>
       </c>
       <c r="N641" t="inlineStr"/>
       <c r="O641" t="inlineStr"/>
@@ -25383,10 +25383,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L642" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M642" t="n">
         <v>719</v>
-      </c>
-      <c r="M642" t="n">
-        <v>0.104</v>
       </c>
       <c r="N642" t="inlineStr"/>
       <c r="O642" t="inlineStr"/>
@@ -25428,10 +25428,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L643" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M643" t="n">
         <v>719</v>
-      </c>
-      <c r="M643" t="n">
-        <v>0.104</v>
       </c>
       <c r="N643" t="inlineStr"/>
       <c r="O643" t="inlineStr"/>
@@ -25473,10 +25473,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L644" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M644" t="n">
         <v>719</v>
-      </c>
-      <c r="M644" t="n">
-        <v>0.104</v>
       </c>
       <c r="N644" t="inlineStr"/>
       <c r="O644" t="inlineStr"/>
@@ -25518,10 +25518,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L645" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M645" t="n">
         <v>719</v>
-      </c>
-      <c r="M645" t="n">
-        <v>0.104</v>
       </c>
       <c r="N645" t="inlineStr"/>
       <c r="O645" t="inlineStr"/>
@@ -25563,10 +25563,10 @@
         <v>0.49034888</v>
       </c>
       <c r="L646" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M646" t="n">
         <v>719</v>
-      </c>
-      <c r="M646" t="n">
-        <v>0.104</v>
       </c>
       <c r="N646" t="inlineStr"/>
       <c r="O646" t="inlineStr"/>
@@ -25607,10 +25607,10 @@
       <c r="K647" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L647" t="inlineStr"/>
-      <c r="M647" t="n">
+      <c r="L647" t="n">
         <v>0.104</v>
       </c>
+      <c r="M647" t="inlineStr"/>
       <c r="N647" t="inlineStr"/>
       <c r="O647" t="inlineStr"/>
       <c r="P647" t="inlineStr"/>
@@ -25650,10 +25650,10 @@
       <c r="K648" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L648" t="inlineStr"/>
-      <c r="M648" t="n">
+      <c r="L648" t="n">
         <v>0.104</v>
       </c>
+      <c r="M648" t="inlineStr"/>
       <c r="N648" t="inlineStr"/>
       <c r="O648" t="inlineStr"/>
       <c r="P648" t="inlineStr"/>
@@ -25693,10 +25693,10 @@
       <c r="K649" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L649" t="inlineStr"/>
-      <c r="M649" t="n">
+      <c r="L649" t="n">
         <v>0.104</v>
       </c>
+      <c r="M649" t="inlineStr"/>
       <c r="N649" t="inlineStr"/>
       <c r="O649" t="inlineStr"/>
       <c r="P649" t="inlineStr"/>
@@ -25736,10 +25736,10 @@
       <c r="K650" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L650" t="inlineStr"/>
-      <c r="M650" t="n">
+      <c r="L650" t="n">
         <v>0.104</v>
       </c>
+      <c r="M650" t="inlineStr"/>
       <c r="N650" t="inlineStr"/>
       <c r="O650" t="inlineStr"/>
       <c r="P650" t="inlineStr"/>
@@ -25779,10 +25779,10 @@
       <c r="K651" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L651" t="inlineStr"/>
-      <c r="M651" t="n">
+      <c r="L651" t="n">
         <v>0.104</v>
       </c>
+      <c r="M651" t="inlineStr"/>
       <c r="N651" t="inlineStr"/>
       <c r="O651" t="inlineStr"/>
       <c r="P651" t="inlineStr"/>
@@ -25822,10 +25822,10 @@
       <c r="K652" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L652" t="inlineStr"/>
-      <c r="M652" t="n">
+      <c r="L652" t="n">
         <v>0.104</v>
       </c>
+      <c r="M652" t="inlineStr"/>
       <c r="N652" t="inlineStr"/>
       <c r="O652" t="inlineStr"/>
       <c r="P652" t="inlineStr"/>
@@ -25865,10 +25865,10 @@
       <c r="K653" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L653" t="inlineStr"/>
-      <c r="M653" t="n">
+      <c r="L653" t="n">
         <v>0.104</v>
       </c>
+      <c r="M653" t="inlineStr"/>
       <c r="N653" t="inlineStr"/>
       <c r="O653" t="inlineStr"/>
       <c r="P653" t="inlineStr"/>
@@ -25908,10 +25908,10 @@
       <c r="K654" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L654" t="inlineStr"/>
-      <c r="M654" t="n">
+      <c r="L654" t="n">
         <v>0.104</v>
       </c>
+      <c r="M654" t="inlineStr"/>
       <c r="N654" t="inlineStr"/>
       <c r="O654" t="inlineStr"/>
       <c r="P654" t="inlineStr"/>
@@ -25951,10 +25951,10 @@
       <c r="K655" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L655" t="inlineStr"/>
-      <c r="M655" t="n">
+      <c r="L655" t="n">
         <v>0.104</v>
       </c>
+      <c r="M655" t="inlineStr"/>
       <c r="N655" t="inlineStr"/>
       <c r="O655" t="inlineStr"/>
       <c r="P655" t="inlineStr"/>
@@ -25994,10 +25994,10 @@
       <c r="K656" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L656" t="inlineStr"/>
-      <c r="M656" t="n">
+      <c r="L656" t="n">
         <v>0.104</v>
       </c>
+      <c r="M656" t="inlineStr"/>
       <c r="N656" t="inlineStr"/>
       <c r="O656" t="inlineStr"/>
       <c r="P656" t="inlineStr"/>
@@ -26037,10 +26037,10 @@
       <c r="K657" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L657" t="inlineStr"/>
-      <c r="M657" t="n">
+      <c r="L657" t="n">
         <v>0.104</v>
       </c>
+      <c r="M657" t="inlineStr"/>
       <c r="N657" t="inlineStr"/>
       <c r="O657" t="inlineStr"/>
       <c r="P657" t="inlineStr"/>
@@ -26080,10 +26080,10 @@
       <c r="K658" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L658" t="inlineStr"/>
-      <c r="M658" t="n">
+      <c r="L658" t="n">
         <v>0.104</v>
       </c>
+      <c r="M658" t="inlineStr"/>
       <c r="N658" t="inlineStr"/>
       <c r="O658" t="inlineStr"/>
       <c r="P658" t="inlineStr"/>
@@ -26123,10 +26123,10 @@
       <c r="K659" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L659" t="inlineStr"/>
-      <c r="M659" t="n">
+      <c r="L659" t="n">
         <v>0.104</v>
       </c>
+      <c r="M659" t="inlineStr"/>
       <c r="N659" t="inlineStr"/>
       <c r="O659" t="inlineStr"/>
       <c r="P659" t="inlineStr"/>
@@ -26166,10 +26166,10 @@
       <c r="K660" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L660" t="inlineStr"/>
-      <c r="M660" t="n">
+      <c r="L660" t="n">
         <v>0.104</v>
       </c>
+      <c r="M660" t="inlineStr"/>
       <c r="N660" t="inlineStr"/>
       <c r="O660" t="inlineStr"/>
       <c r="P660" t="inlineStr"/>
@@ -26209,10 +26209,10 @@
       <c r="K661" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L661" t="inlineStr"/>
-      <c r="M661" t="n">
+      <c r="L661" t="n">
         <v>0.104</v>
       </c>
+      <c r="M661" t="inlineStr"/>
       <c r="N661" t="inlineStr"/>
       <c r="O661" t="inlineStr"/>
       <c r="P661" t="inlineStr"/>
@@ -26252,10 +26252,10 @@
       <c r="K662" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L662" t="inlineStr"/>
-      <c r="M662" t="n">
+      <c r="L662" t="n">
         <v>0.104</v>
       </c>
+      <c r="M662" t="inlineStr"/>
       <c r="N662" t="inlineStr"/>
       <c r="O662" t="inlineStr"/>
       <c r="P662" t="inlineStr"/>
@@ -26295,10 +26295,10 @@
       <c r="K663" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L663" t="inlineStr"/>
-      <c r="M663" t="n">
+      <c r="L663" t="n">
         <v>0.104</v>
       </c>
+      <c r="M663" t="inlineStr"/>
       <c r="N663" t="inlineStr"/>
       <c r="O663" t="inlineStr"/>
       <c r="P663" t="inlineStr"/>
@@ -26338,10 +26338,10 @@
       <c r="K664" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L664" t="inlineStr"/>
-      <c r="M664" t="n">
+      <c r="L664" t="n">
         <v>0.104</v>
       </c>
+      <c r="M664" t="inlineStr"/>
       <c r="N664" t="inlineStr"/>
       <c r="O664" t="inlineStr"/>
       <c r="P664" t="inlineStr"/>
@@ -26381,10 +26381,10 @@
       <c r="K665" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L665" t="inlineStr"/>
-      <c r="M665" t="n">
+      <c r="L665" t="n">
         <v>0.104</v>
       </c>
+      <c r="M665" t="inlineStr"/>
       <c r="N665" t="inlineStr"/>
       <c r="O665" t="inlineStr"/>
       <c r="P665" t="inlineStr"/>
@@ -26424,10 +26424,10 @@
       <c r="K666" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L666" t="inlineStr"/>
-      <c r="M666" t="n">
+      <c r="L666" t="n">
         <v>0.104</v>
       </c>
+      <c r="M666" t="inlineStr"/>
       <c r="N666" t="inlineStr"/>
       <c r="O666" t="inlineStr"/>
       <c r="P666" t="inlineStr"/>
@@ -26467,10 +26467,10 @@
       <c r="K667" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L667" t="inlineStr"/>
-      <c r="M667" t="n">
+      <c r="L667" t="n">
         <v>0.104</v>
       </c>
+      <c r="M667" t="inlineStr"/>
       <c r="N667" t="inlineStr"/>
       <c r="O667" t="inlineStr"/>
       <c r="P667" t="inlineStr"/>
@@ -26510,10 +26510,10 @@
       <c r="K668" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L668" t="inlineStr"/>
-      <c r="M668" t="n">
+      <c r="L668" t="n">
         <v>0.104</v>
       </c>
+      <c r="M668" t="inlineStr"/>
       <c r="N668" t="inlineStr"/>
       <c r="O668" t="inlineStr"/>
       <c r="P668" t="inlineStr"/>
@@ -26553,10 +26553,10 @@
       <c r="K669" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L669" t="inlineStr"/>
-      <c r="M669" t="n">
+      <c r="L669" t="n">
         <v>0.104</v>
       </c>
+      <c r="M669" t="inlineStr"/>
       <c r="N669" t="inlineStr"/>
       <c r="O669" t="inlineStr"/>
       <c r="P669" t="inlineStr"/>
@@ -26596,10 +26596,10 @@
       <c r="K670" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L670" t="inlineStr"/>
-      <c r="M670" t="n">
+      <c r="L670" t="n">
         <v>0.104</v>
       </c>
+      <c r="M670" t="inlineStr"/>
       <c r="N670" t="inlineStr"/>
       <c r="O670" t="inlineStr"/>
       <c r="P670" t="inlineStr"/>
@@ -26639,15 +26639,187 @@
       <c r="K671" t="n">
         <v>0.02386888</v>
       </c>
-      <c r="L671" t="inlineStr"/>
-      <c r="M671" t="n">
+      <c r="L671" t="n">
         <v>0.104</v>
       </c>
+      <c r="M671" t="inlineStr"/>
       <c r="N671" t="inlineStr"/>
       <c r="O671" t="inlineStr"/>
       <c r="P671" t="inlineStr"/>
       <c r="Q671" t="inlineStr"/>
     </row>
+    <row r="672">
+      <c r="A672" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B672" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C672" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D672" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E672" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F672" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G672" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H672" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I672" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J672" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K672" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L672" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M672" t="inlineStr"/>
+      <c r="N672" t="inlineStr"/>
+      <c r="O672" t="inlineStr"/>
+      <c r="P672" t="inlineStr"/>
+      <c r="Q672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B673" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C673" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D673" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E673" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F673" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G673" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H673" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I673" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J673" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K673" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L673" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M673" t="inlineStr"/>
+      <c r="N673" t="inlineStr"/>
+      <c r="O673" t="inlineStr"/>
+      <c r="P673" t="inlineStr"/>
+      <c r="Q673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B674" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C674" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D674" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E674" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F674" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G674" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H674" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I674" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J674" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K674" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L674" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M674" t="inlineStr"/>
+      <c r="N674" t="inlineStr"/>
+      <c r="O674" t="inlineStr"/>
+      <c r="P674" t="inlineStr"/>
+      <c r="Q674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B675" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C675" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D675" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E675" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F675" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G675" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H675" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I675" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J675" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K675" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L675" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M675" t="inlineStr"/>
+      <c r="N675" t="inlineStr"/>
+      <c r="O675" t="inlineStr"/>
+      <c r="P675" t="inlineStr"/>
+      <c r="Q675" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q675"/>
+  <dimension ref="A1:Q676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26820,6 +26820,49 @@
       <c r="P675" t="inlineStr"/>
       <c r="Q675" t="inlineStr"/>
     </row>
+    <row r="676">
+      <c r="A676" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B676" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C676" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D676" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E676" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G676" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H676" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I676" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J676" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K676" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L676" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M676" t="inlineStr"/>
+      <c r="N676" t="inlineStr"/>
+      <c r="O676" t="inlineStr"/>
+      <c r="P676" t="inlineStr"/>
+      <c r="Q676" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q676"/>
+  <dimension ref="A1:Q677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26863,6 +26863,49 @@
       <c r="P676" t="inlineStr"/>
       <c r="Q676" t="inlineStr"/>
     </row>
+    <row r="677">
+      <c r="A677" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B677" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C677" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D677" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E677" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F677" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G677" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H677" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I677" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J677" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K677" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L677" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M677" t="inlineStr"/>
+      <c r="N677" t="inlineStr"/>
+      <c r="O677" t="inlineStr"/>
+      <c r="P677" t="inlineStr"/>
+      <c r="Q677" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q677"/>
+  <dimension ref="A1:Q678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26906,6 +26906,49 @@
       <c r="P677" t="inlineStr"/>
       <c r="Q677" t="inlineStr"/>
     </row>
+    <row r="678">
+      <c r="A678" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B678" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C678" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D678" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E678" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F678" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G678" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H678" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I678" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J678" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K678" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L678" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M678" t="inlineStr"/>
+      <c r="N678" t="inlineStr"/>
+      <c r="O678" t="inlineStr"/>
+      <c r="P678" t="inlineStr"/>
+      <c r="Q678" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q678"/>
+  <dimension ref="A1:Q680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26949,6 +26949,92 @@
       <c r="P678" t="inlineStr"/>
       <c r="Q678" t="inlineStr"/>
     </row>
+    <row r="679">
+      <c r="A679" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B679" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C679" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D679" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E679" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F679" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G679" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H679" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I679" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J679" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K679" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L679" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M679" t="inlineStr"/>
+      <c r="N679" t="inlineStr"/>
+      <c r="O679" t="inlineStr"/>
+      <c r="P679" t="inlineStr"/>
+      <c r="Q679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="2" t="n">
+        <v>46236</v>
+      </c>
+      <c r="B680" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C680" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D680" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E680" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F680" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G680" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H680" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I680" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J680" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K680" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L680" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M680" t="inlineStr"/>
+      <c r="N680" t="inlineStr"/>
+      <c r="O680" t="inlineStr"/>
+      <c r="P680" t="inlineStr"/>
+      <c r="Q680" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q680"/>
+  <dimension ref="A1:Q682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27035,6 +27035,92 @@
       <c r="P680" t="inlineStr"/>
       <c r="Q680" t="inlineStr"/>
     </row>
+    <row r="681">
+      <c r="A681" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B681" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C681" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D681" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E681" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F681" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G681" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H681" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I681" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J681" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K681" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L681" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M681" t="inlineStr"/>
+      <c r="N681" t="inlineStr"/>
+      <c r="O681" t="inlineStr"/>
+      <c r="P681" t="inlineStr"/>
+      <c r="Q681" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B682" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C682" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D682" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E682" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G682" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H682" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I682" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J682" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K682" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L682" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M682" t="inlineStr"/>
+      <c r="N682" t="inlineStr"/>
+      <c r="O682" t="inlineStr"/>
+      <c r="P682" t="inlineStr"/>
+      <c r="Q682" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q682"/>
+  <dimension ref="A1:Q684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27121,6 +27121,92 @@
       <c r="P682" t="inlineStr"/>
       <c r="Q682" t="inlineStr"/>
     </row>
+    <row r="683">
+      <c r="A683" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B683" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C683" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D683" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E683" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F683" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G683" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H683" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I683" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J683" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K683" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L683" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M683" t="inlineStr"/>
+      <c r="N683" t="inlineStr"/>
+      <c r="O683" t="inlineStr"/>
+      <c r="P683" t="inlineStr"/>
+      <c r="Q683" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B684" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C684" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D684" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E684" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F684" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G684" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H684" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I684" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J684" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K684" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L684" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M684" t="inlineStr"/>
+      <c r="N684" t="inlineStr"/>
+      <c r="O684" t="inlineStr"/>
+      <c r="P684" t="inlineStr"/>
+      <c r="Q684" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q684"/>
+  <dimension ref="A1:Q685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27207,6 +27207,49 @@
       <c r="P684" t="inlineStr"/>
       <c r="Q684" t="inlineStr"/>
     </row>
+    <row r="685">
+      <c r="A685" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B685" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C685" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D685" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E685" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G685" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H685" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I685" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J685" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K685" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L685" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M685" t="inlineStr"/>
+      <c r="N685" t="inlineStr"/>
+      <c r="O685" t="inlineStr"/>
+      <c r="P685" t="inlineStr"/>
+      <c r="Q685" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q685"/>
+  <dimension ref="A1:Q686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27250,6 +27250,49 @@
       <c r="P685" t="inlineStr"/>
       <c r="Q685" t="inlineStr"/>
     </row>
+    <row r="686">
+      <c r="A686" s="2" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B686" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C686" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D686" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E686" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F686" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G686" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H686" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I686" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J686" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K686" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L686" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M686" t="inlineStr"/>
+      <c r="N686" t="inlineStr"/>
+      <c r="O686" t="inlineStr"/>
+      <c r="P686" t="inlineStr"/>
+      <c r="Q686" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q686"/>
+  <dimension ref="A1:Q688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27293,6 +27293,92 @@
       <c r="P686" t="inlineStr"/>
       <c r="Q686" t="inlineStr"/>
     </row>
+    <row r="687">
+      <c r="A687" s="2" t="n">
+        <v>46243</v>
+      </c>
+      <c r="B687" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C687" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D687" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E687" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F687" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G687" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H687" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I687" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J687" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K687" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L687" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M687" t="inlineStr"/>
+      <c r="N687" t="inlineStr"/>
+      <c r="O687" t="inlineStr"/>
+      <c r="P687" t="inlineStr"/>
+      <c r="Q687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B688" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C688" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D688" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E688" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G688" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H688" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I688" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J688" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K688" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L688" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M688" t="inlineStr"/>
+      <c r="N688" t="inlineStr"/>
+      <c r="O688" t="inlineStr"/>
+      <c r="P688" t="inlineStr"/>
+      <c r="Q688" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q688"/>
+  <dimension ref="A1:Q691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27379,6 +27379,135 @@
       <c r="P688" t="inlineStr"/>
       <c r="Q688" t="inlineStr"/>
     </row>
+    <row r="689">
+      <c r="A689" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B689" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C689" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D689" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E689" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G689" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H689" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I689" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J689" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K689" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L689" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M689" t="inlineStr"/>
+      <c r="N689" t="inlineStr"/>
+      <c r="O689" t="inlineStr"/>
+      <c r="P689" t="inlineStr"/>
+      <c r="Q689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B690" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C690" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D690" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E690" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F690" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G690" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H690" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I690" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J690" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K690" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L690" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M690" t="inlineStr"/>
+      <c r="N690" t="inlineStr"/>
+      <c r="O690" t="inlineStr"/>
+      <c r="P690" t="inlineStr"/>
+      <c r="Q690" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B691" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C691" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D691" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E691" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G691" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H691" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I691" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J691" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K691" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L691" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M691" t="inlineStr"/>
+      <c r="N691" t="inlineStr"/>
+      <c r="O691" t="inlineStr"/>
+      <c r="P691" t="inlineStr"/>
+      <c r="Q691" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q691"/>
+  <dimension ref="A1:Q693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27508,6 +27508,92 @@
       <c r="P691" t="inlineStr"/>
       <c r="Q691" t="inlineStr"/>
     </row>
+    <row r="692">
+      <c r="A692" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B692" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C692" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D692" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E692" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G692" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H692" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I692" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J692" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K692" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L692" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M692" t="inlineStr"/>
+      <c r="N692" t="inlineStr"/>
+      <c r="O692" t="inlineStr"/>
+      <c r="P692" t="inlineStr"/>
+      <c r="Q692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="2" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B693" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C693" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D693" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E693" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G693" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H693" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I693" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J693" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K693" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L693" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M693" t="inlineStr"/>
+      <c r="N693" t="inlineStr"/>
+      <c r="O693" t="inlineStr"/>
+      <c r="P693" t="inlineStr"/>
+      <c r="Q693" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q693"/>
+  <dimension ref="A1:Q694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27594,6 +27594,49 @@
       <c r="P693" t="inlineStr"/>
       <c r="Q693" t="inlineStr"/>
     </row>
+    <row r="694">
+      <c r="A694" s="2" t="n">
+        <v>46250</v>
+      </c>
+      <c r="B694" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C694" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D694" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E694" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F694" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G694" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H694" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I694" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J694" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K694" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L694" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M694" t="inlineStr"/>
+      <c r="N694" t="inlineStr"/>
+      <c r="O694" t="inlineStr"/>
+      <c r="P694" t="inlineStr"/>
+      <c r="Q694" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q694"/>
+  <dimension ref="A1:Q695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27637,6 +27637,49 @@
       <c r="P694" t="inlineStr"/>
       <c r="Q694" t="inlineStr"/>
     </row>
+    <row r="695">
+      <c r="A695" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B695" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C695" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D695" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E695" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F695" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G695" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H695" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I695" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J695" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K695" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L695" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M695" t="inlineStr"/>
+      <c r="N695" t="inlineStr"/>
+      <c r="O695" t="inlineStr"/>
+      <c r="P695" t="inlineStr"/>
+      <c r="Q695" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q695"/>
+  <dimension ref="A1:Q696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27680,6 +27680,49 @@
       <c r="P695" t="inlineStr"/>
       <c r="Q695" t="inlineStr"/>
     </row>
+    <row r="696">
+      <c r="A696" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B696" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C696" t="n">
+        <v>0.00023768</v>
+      </c>
+      <c r="D696" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E696" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F696" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G696" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H696" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I696" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J696" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K696" t="n">
+        <v>0.02386888</v>
+      </c>
+      <c r="L696" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="M696" t="inlineStr"/>
+      <c r="N696" t="inlineStr"/>
+      <c r="O696" t="inlineStr"/>
+      <c r="P696" t="inlineStr"/>
+      <c r="Q696" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q696"/>
+  <dimension ref="A1:Q699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27723,6 +27723,129 @@
       <c r="P696" t="inlineStr"/>
       <c r="Q696" t="inlineStr"/>
     </row>
+    <row r="697">
+      <c r="A697" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B697" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C697" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="D697" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E697" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F697" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G697" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H697" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I697" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J697" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K697" t="n">
+        <v>58.64456888</v>
+      </c>
+      <c r="L697" t="inlineStr"/>
+      <c r="M697" t="inlineStr"/>
+      <c r="N697" t="inlineStr"/>
+      <c r="O697" t="inlineStr"/>
+      <c r="P697" t="inlineStr"/>
+      <c r="Q697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B698" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C698" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="D698" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E698" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F698" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G698" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H698" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I698" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J698" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K698" t="n">
+        <v>58.64456888</v>
+      </c>
+      <c r="L698" t="inlineStr"/>
+      <c r="M698" t="inlineStr"/>
+      <c r="N698" t="inlineStr"/>
+      <c r="O698" t="inlineStr"/>
+      <c r="P698" t="inlineStr"/>
+      <c r="Q698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B699" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C699" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="D699" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E699" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F699" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G699" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H699" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I699" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J699" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K699" t="n">
+        <v>58.64456888</v>
+      </c>
+      <c r="L699" t="inlineStr"/>
+      <c r="M699" t="inlineStr"/>
+      <c r="N699" t="inlineStr"/>
+      <c r="O699" t="inlineStr"/>
+      <c r="P699" t="inlineStr"/>
+      <c r="Q699" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q699"/>
+  <dimension ref="A1:Q700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27846,6 +27846,47 @@
       <c r="P699" t="inlineStr"/>
       <c r="Q699" t="inlineStr"/>
     </row>
+    <row r="700">
+      <c r="A700" s="2" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B700" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C700" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="D700" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E700" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G700" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H700" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I700" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J700" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K700" t="n">
+        <v>58.64456888</v>
+      </c>
+      <c r="L700" t="inlineStr"/>
+      <c r="M700" t="inlineStr"/>
+      <c r="N700" t="inlineStr"/>
+      <c r="O700" t="inlineStr"/>
+      <c r="P700" t="inlineStr"/>
+      <c r="Q700" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q700"/>
+  <dimension ref="A1:Q701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27887,6 +27887,47 @@
       <c r="P700" t="inlineStr"/>
       <c r="Q700" t="inlineStr"/>
     </row>
+    <row r="701">
+      <c r="A701" s="2" t="n">
+        <v>46257</v>
+      </c>
+      <c r="B701" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C701" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="D701" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E701" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F701" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G701" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H701" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I701" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J701" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K701" t="n">
+        <v>58.64456888</v>
+      </c>
+      <c r="L701" t="inlineStr"/>
+      <c r="M701" t="inlineStr"/>
+      <c r="N701" t="inlineStr"/>
+      <c r="O701" t="inlineStr"/>
+      <c r="P701" t="inlineStr"/>
+      <c r="Q701" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q701"/>
+  <dimension ref="A1:Q702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27928,6 +27928,47 @@
       <c r="P701" t="inlineStr"/>
       <c r="Q701" t="inlineStr"/>
     </row>
+    <row r="702">
+      <c r="A702" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B702" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C702" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="D702" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E702" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G702" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H702" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I702" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J702" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K702" t="n">
+        <v>58.64456888</v>
+      </c>
+      <c r="L702" t="inlineStr"/>
+      <c r="M702" t="inlineStr"/>
+      <c r="N702" t="inlineStr"/>
+      <c r="O702" t="inlineStr"/>
+      <c r="P702" t="inlineStr"/>
+      <c r="Q702" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q702"/>
+  <dimension ref="A1:Q703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27969,6 +27969,47 @@
       <c r="P702" t="inlineStr"/>
       <c r="Q702" t="inlineStr"/>
     </row>
+    <row r="703">
+      <c r="A703" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B703" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C703" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="D703" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E703" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F703" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G703" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H703" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I703" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J703" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K703" t="n">
+        <v>58.64456888</v>
+      </c>
+      <c r="L703" t="inlineStr"/>
+      <c r="M703" t="inlineStr"/>
+      <c r="N703" t="inlineStr"/>
+      <c r="O703" t="inlineStr"/>
+      <c r="P703" t="inlineStr"/>
+      <c r="Q703" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q703"/>
+  <dimension ref="A1:Q704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28010,6 +28010,47 @@
       <c r="P703" t="inlineStr"/>
       <c r="Q703" t="inlineStr"/>
     </row>
+    <row r="704">
+      <c r="A704" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B704" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C704" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="D704" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E704" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F704" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G704" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H704" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I704" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J704" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K704" t="n">
+        <v>58.64456888</v>
+      </c>
+      <c r="L704" t="inlineStr"/>
+      <c r="M704" t="inlineStr"/>
+      <c r="N704" t="inlineStr"/>
+      <c r="O704" t="inlineStr"/>
+      <c r="P704" t="inlineStr"/>
+      <c r="Q704" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q704"/>
+  <dimension ref="A1:Q705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28051,6 +28051,47 @@
       <c r="P704" t="inlineStr"/>
       <c r="Q704" t="inlineStr"/>
     </row>
+    <row r="705">
+      <c r="A705" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B705" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C705" t="n">
+        <v>0.000171</v>
+      </c>
+      <c r="D705" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E705" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F705" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G705" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H705" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I705" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J705" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K705" t="n">
+        <v>58.64456888</v>
+      </c>
+      <c r="L705" t="inlineStr"/>
+      <c r="M705" t="inlineStr"/>
+      <c r="N705" t="inlineStr"/>
+      <c r="O705" t="inlineStr"/>
+      <c r="P705" t="inlineStr"/>
+      <c r="Q705" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q705"/>
+  <dimension ref="A1:Q706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28092,6 +28092,49 @@
       <c r="P705" t="inlineStr"/>
       <c r="Q705" t="inlineStr"/>
     </row>
+    <row r="706">
+      <c r="A706" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B706" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C706" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D706" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E706" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F706" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G706" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H706" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I706" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J706" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K706" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L706" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M706" t="inlineStr"/>
+      <c r="N706" t="inlineStr"/>
+      <c r="O706" t="inlineStr"/>
+      <c r="P706" t="inlineStr"/>
+      <c r="Q706" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q706"/>
+  <dimension ref="A1:Q707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28135,6 +28135,49 @@
       <c r="P706" t="inlineStr"/>
       <c r="Q706" t="inlineStr"/>
     </row>
+    <row r="707">
+      <c r="A707" s="2" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B707" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C707" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D707" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E707" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F707" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G707" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H707" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I707" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J707" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K707" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L707" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M707" t="inlineStr"/>
+      <c r="N707" t="inlineStr"/>
+      <c r="O707" t="inlineStr"/>
+      <c r="P707" t="inlineStr"/>
+      <c r="Q707" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q707"/>
+  <dimension ref="A1:Q708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28178,6 +28178,49 @@
       <c r="P707" t="inlineStr"/>
       <c r="Q707" t="inlineStr"/>
     </row>
+    <row r="708">
+      <c r="A708" s="2" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B708" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C708" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D708" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E708" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F708" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G708" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H708" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I708" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J708" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K708" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L708" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M708" t="inlineStr"/>
+      <c r="N708" t="inlineStr"/>
+      <c r="O708" t="inlineStr"/>
+      <c r="P708" t="inlineStr"/>
+      <c r="Q708" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q708"/>
+  <dimension ref="A1:Q710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28221,6 +28221,92 @@
       <c r="P708" t="inlineStr"/>
       <c r="Q708" t="inlineStr"/>
     </row>
+    <row r="709">
+      <c r="A709" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B709" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C709" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D709" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E709" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F709" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G709" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H709" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I709" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J709" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K709" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L709" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M709" t="inlineStr"/>
+      <c r="N709" t="inlineStr"/>
+      <c r="O709" t="inlineStr"/>
+      <c r="P709" t="inlineStr"/>
+      <c r="Q709" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B710" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C710" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D710" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E710" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F710" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G710" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H710" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I710" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J710" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K710" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L710" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M710" t="inlineStr"/>
+      <c r="N710" t="inlineStr"/>
+      <c r="O710" t="inlineStr"/>
+      <c r="P710" t="inlineStr"/>
+      <c r="Q710" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q710"/>
+  <dimension ref="A1:Q711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28307,6 +28307,49 @@
       <c r="P710" t="inlineStr"/>
       <c r="Q710" t="inlineStr"/>
     </row>
+    <row r="711">
+      <c r="A711" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B711" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C711" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D711" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E711" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F711" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G711" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H711" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I711" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J711" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K711" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L711" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M711" t="inlineStr"/>
+      <c r="N711" t="inlineStr"/>
+      <c r="O711" t="inlineStr"/>
+      <c r="P711" t="inlineStr"/>
+      <c r="Q711" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q711"/>
+  <dimension ref="A1:Q712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28350,6 +28350,49 @@
       <c r="P711" t="inlineStr"/>
       <c r="Q711" t="inlineStr"/>
     </row>
+    <row r="712">
+      <c r="A712" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B712" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C712" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D712" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E712" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F712" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G712" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H712" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I712" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J712" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K712" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L712" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M712" t="inlineStr"/>
+      <c r="N712" t="inlineStr"/>
+      <c r="O712" t="inlineStr"/>
+      <c r="P712" t="inlineStr"/>
+      <c r="Q712" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q712"/>
+  <dimension ref="A1:Q713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28393,6 +28393,49 @@
       <c r="P712" t="inlineStr"/>
       <c r="Q712" t="inlineStr"/>
     </row>
+    <row r="713">
+      <c r="A713" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B713" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C713" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D713" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E713" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F713" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G713" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H713" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I713" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J713" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K713" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L713" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M713" t="inlineStr"/>
+      <c r="N713" t="inlineStr"/>
+      <c r="O713" t="inlineStr"/>
+      <c r="P713" t="inlineStr"/>
+      <c r="Q713" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q713"/>
+  <dimension ref="A1:Q714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28436,6 +28436,49 @@
       <c r="P713" t="inlineStr"/>
       <c r="Q713" t="inlineStr"/>
     </row>
+    <row r="714">
+      <c r="A714" s="2" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B714" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C714" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D714" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E714" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F714" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G714" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H714" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I714" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J714" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K714" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L714" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M714" t="inlineStr"/>
+      <c r="N714" t="inlineStr"/>
+      <c r="O714" t="inlineStr"/>
+      <c r="P714" t="inlineStr"/>
+      <c r="Q714" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q714"/>
+  <dimension ref="A1:Q715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28479,6 +28479,49 @@
       <c r="P714" t="inlineStr"/>
       <c r="Q714" t="inlineStr"/>
     </row>
+    <row r="715">
+      <c r="A715" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B715" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C715" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D715" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E715" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F715" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G715" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H715" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I715" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J715" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K715" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L715" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M715" t="inlineStr"/>
+      <c r="N715" t="inlineStr"/>
+      <c r="O715" t="inlineStr"/>
+      <c r="P715" t="inlineStr"/>
+      <c r="Q715" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q715"/>
+  <dimension ref="A1:Q716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28522,6 +28522,49 @@
       <c r="P715" t="inlineStr"/>
       <c r="Q715" t="inlineStr"/>
     </row>
+    <row r="716">
+      <c r="A716" s="2" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B716" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C716" t="n">
+        <v>0.00011201</v>
+      </c>
+      <c r="D716" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E716" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F716" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G716" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H716" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I716" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J716" t="n">
+        <v>4909.25449423</v>
+      </c>
+      <c r="K716" t="n">
+        <v>0.32146888</v>
+      </c>
+      <c r="L716" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="M716" t="inlineStr"/>
+      <c r="N716" t="inlineStr"/>
+      <c r="O716" t="inlineStr"/>
+      <c r="P716" t="inlineStr"/>
+      <c r="Q716" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q716"/>
+  <dimension ref="A1:Q717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28565,6 +28565,49 @@
       <c r="P716" t="inlineStr"/>
       <c r="Q716" t="inlineStr"/>
     </row>
+    <row r="717">
+      <c r="A717" s="2" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B717" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C717" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D717" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E717" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F717" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G717" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H717" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I717" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J717" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K717" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L717" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M717" t="inlineStr"/>
+      <c r="N717" t="inlineStr"/>
+      <c r="O717" t="inlineStr"/>
+      <c r="P717" t="inlineStr"/>
+      <c r="Q717" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q717"/>
+  <dimension ref="A1:Q719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28608,6 +28608,92 @@
       <c r="P717" t="inlineStr"/>
       <c r="Q717" t="inlineStr"/>
     </row>
+    <row r="718">
+      <c r="A718" s="2" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B718" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C718" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D718" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E718" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F718" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G718" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H718" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I718" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J718" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K718" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L718" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M718" t="inlineStr"/>
+      <c r="N718" t="inlineStr"/>
+      <c r="O718" t="inlineStr"/>
+      <c r="P718" t="inlineStr"/>
+      <c r="Q718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B719" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C719" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D719" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E719" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F719" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G719" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H719" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I719" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J719" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K719" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L719" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M719" t="inlineStr"/>
+      <c r="N719" t="inlineStr"/>
+      <c r="O719" t="inlineStr"/>
+      <c r="P719" t="inlineStr"/>
+      <c r="Q719" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q719"/>
+  <dimension ref="A1:Q720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28694,6 +28694,49 @@
       <c r="P719" t="inlineStr"/>
       <c r="Q719" t="inlineStr"/>
     </row>
+    <row r="720">
+      <c r="A720" s="2" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B720" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C720" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D720" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E720" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F720" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G720" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H720" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I720" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J720" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K720" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L720" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M720" t="inlineStr"/>
+      <c r="N720" t="inlineStr"/>
+      <c r="O720" t="inlineStr"/>
+      <c r="P720" t="inlineStr"/>
+      <c r="Q720" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
